--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19305" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Info'!$B$540</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Info'!$B$539</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -798,8 +798,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN530" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN530"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN529" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="B1:AN529"/>
   <tableColumns count="39">
     <tableColumn id="1" name="Client ID"/>
     <tableColumn id="2" name="Client"/>
@@ -1150,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R530"/>
+  <dimension ref="A1:R529"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="15.7109375" customWidth="1" min="1" max="1"/>
@@ -1191,7 +1191,7 @@
     <col width="33.28515625" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28.9" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
     </row>
-    <row r="2" customFormat="1" s="62">
+    <row r="2" ht="14.45" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1367,7 +1367,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.45" customHeight="1">
       <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1521,7 +1521,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="28.9" customHeight="1">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="14.45" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1640,7 +1640,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.45" customHeight="1">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.45" customHeight="1">
       <c r="B8" s="27" t="n">
         <v>3007</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="Q8" s="108" t="n"/>
       <c r="R8" s="66" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="14.45" customHeight="1">
       <c r="B9" t="n">
         <v>3008</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>45516</v>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="43.15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2074,7 +2074,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="13" customFormat="1" s="27">
+    <row r="13" ht="14.45" customFormat="1" customHeight="1" s="27">
       <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2138,7 +2138,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.45" customHeight="1">
       <c r="B14" s="27" t="n">
         <v>3012</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="Q14" s="108" t="n"/>
       <c r="R14" s="66" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14.45" customHeight="1">
       <c r="B15" s="27" t="n">
         <v>3013</v>
       </c>
@@ -2180,7 +2180,7 @@
       <c r="Q15" s="108" t="n"/>
       <c r="R15" s="66" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="14.45" customHeight="1">
       <c r="B16" t="n">
         <v>3014</v>
       </c>
@@ -2484,7 +2484,7 @@
       <c r="Q19" s="88" t="n"/>
       <c r="R19" s="23" t="n"/>
     </row>
-    <row r="20" ht="45" customFormat="1" customHeight="1" s="27">
+    <row r="20" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2529,7 +2529,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="21" ht="45" customFormat="1" customHeight="1" s="27">
+    <row r="21" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B21" t="n">
         <v>3018</v>
       </c>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customFormat="1" customHeight="1" s="27">
+    <row r="22" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B22" t="n">
         <v>3019</v>
       </c>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="43.15" customHeight="1">
       <c r="B23" t="n">
         <v>3020</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="26" ht="30.75" customHeight="1">
+    <row r="26" ht="28.9" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2861,7 +2861,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="28.9" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="45.75" customHeight="1" thickBot="1">
+    <row r="28" ht="43.9" customHeight="1" thickBot="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Q28" s="4" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="14.45" customHeight="1">
       <c r="B29" t="n">
         <v>3026</v>
       </c>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Q29" s="4" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="14.45" customHeight="1">
       <c r="B30" t="n">
         <v>3026</v>
       </c>
@@ -3103,7 +3103,7 @@
       <c r="O30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="14.45" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="28.9" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="43.15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="28.9" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="43.15" customHeight="1">
       <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3499,7 +3499,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="43.15" customHeight="1">
       <c r="B37" t="n">
         <v>3035</v>
       </c>
@@ -3568,7 +3568,7 @@
       <c r="O37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="57.6" customHeight="1">
       <c r="B38" t="n">
         <v>3035</v>
       </c>
@@ -3633,7 +3633,7 @@
       <c r="O38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
     </row>
-    <row r="39" customFormat="1" s="138">
+    <row r="39" ht="14.45" customFormat="1" customHeight="1" s="138">
       <c r="A39" s="138" t="inlineStr">
         <is>
           <t>QL</t>
@@ -3702,7 +3702,7 @@
       <c r="O39" s="140" t="n"/>
       <c r="Q39" s="140" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="14.45" customHeight="1">
       <c r="B40" t="n">
         <v>3031</v>
       </c>
@@ -3769,7 +3769,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41" ht="57.6" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="28.9" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3909,7 +3909,7 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" ht="45" customHeight="1">
+    <row r="43" ht="43.15" customHeight="1">
       <c r="B43" t="n">
         <v>3035</v>
       </c>
@@ -3953,7 +3953,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="28.9" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="14.45" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>US</t>
@@ -4059,7 +4059,7 @@
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" ht="40.5" customHeight="1">
+    <row r="46" ht="41.45" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4119,7 +4119,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="28.9" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4182,7 +4182,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="14.45" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4239,7 +4239,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" ht="45" customHeight="1">
+    <row r="49" ht="43.15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>US</t>
@@ -4283,7 +4283,7 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" customFormat="1" s="138">
+    <row r="50" ht="14.45" customFormat="1" customHeight="1" s="138">
       <c r="A50" s="138" t="inlineStr">
         <is>
           <t>QL</t>
@@ -4352,7 +4352,7 @@
       <c r="O50" s="140" t="n"/>
       <c r="Q50" s="140" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="14.45" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4379,7 +4379,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="14.45" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4436,7 +4436,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="14.45" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4463,7 +4463,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="14.45" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4495,7 +4495,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="14.45" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4527,7 +4527,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="14.45" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4559,7 +4559,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="14.45" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4591,7 +4591,7 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="14.45" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4623,7 +4623,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="14.45" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4655,31 +4655,50 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="14.45" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3000</v>
+        <v>3052</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : MACDERMID</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
       </c>
       <c r="O60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
-      <c r="R60" s="23" t="n"/>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" ht="14.45" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : MACDERMID</t>
+          <t>Castellbisbal multi client : ENGIPLASTE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4700,18 +4719,18 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="14.45" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : ENGIPLASTE</t>
+          <t>Castellbisbal multi client : GLOKEM</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4732,18 +4751,18 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="14.45" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : GLOKEM</t>
+          <t>Castellbisbal multi client : QUIMICALITE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4764,55 +4783,60 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="64" ht="14.45" customHeight="1">
       <c r="B64" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : QUIMICALITE</t>
+          <t>Riviana</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NP9</t>
+          <t>NP38</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ES01</t>
+          <t>WIL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>bh10</t>
+          <t>be40</t>
         </is>
       </c>
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="43.15" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="B65" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Riviana</t>
+          <t>Davine's Spa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NP38</t>
+          <t>NP40</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BY Case 05787176</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>WIL</t>
+          <t>MP1</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4820,54 +4844,61 @@
           <t>be40</t>
         </is>
       </c>
-      <c r="O65" s="4" t="n"/>
-      <c r="Q65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>3057</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Davine's Spa</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NP40</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>BY Case 05787176</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>MP1</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>336 Heinz St
 Mechanicsburg, PA 17055
 USA</t>
         </is>
       </c>
-      <c r="O66" s="4" t="n"/>
-      <c r="Q66" s="4" t="n"/>
-    </row>
-    <row r="67" customFormat="1" s="138">
+      <c r="O65" s="4" t="n"/>
+      <c r="Q65" s="4" t="n"/>
+    </row>
+    <row r="66" ht="14.45" customFormat="1" customHeight="1" s="138">
+      <c r="A66" s="138" t="inlineStr">
+        <is>
+          <t>QL</t>
+        </is>
+      </c>
+      <c r="B66" s="139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="138" t="inlineStr">
+        <is>
+          <t>QL Dev/Test Env for NP5</t>
+        </is>
+      </c>
+      <c r="D66" s="138" t="inlineStr">
+        <is>
+          <t>NP14</t>
+        </is>
+      </c>
+      <c r="E66" s="138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F66" s="138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G66" s="138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H66" s="138" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O66" s="140" t="n"/>
+      <c r="Q66" s="140" t="n"/>
+    </row>
+    <row r="67" ht="14.45" customFormat="1" customHeight="1" s="138">
       <c r="A67" s="138" t="inlineStr">
         <is>
           <t>QL</t>
@@ -4880,12 +4911,12 @@
       </c>
       <c r="C67" s="138" t="inlineStr">
         <is>
-          <t>QL Dev/Test Env for NP5</t>
+          <t>QL DEV/Test Env for NP25</t>
         </is>
       </c>
       <c r="D67" s="138" t="inlineStr">
         <is>
-          <t>NP14</t>
+          <t>NP39</t>
         </is>
       </c>
       <c r="E67" s="138" t="inlineStr">
@@ -4905,117 +4936,105 @@
       </c>
       <c r="H67" s="138" t="inlineStr">
         <is>
-          <t>bh10</t>
+          <t>be40</t>
         </is>
       </c>
       <c r="O67" s="140" t="n"/>
       <c r="Q67" s="140" t="n"/>
     </row>
-    <row r="68" customFormat="1" s="138">
-      <c r="A68" s="138" t="inlineStr">
-        <is>
-          <t>QL</t>
-        </is>
-      </c>
-      <c r="B68" s="139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="138" t="inlineStr">
-        <is>
-          <t>QL DEV/Test Env for NP25</t>
-        </is>
-      </c>
-      <c r="D68" s="138" t="inlineStr">
-        <is>
-          <t>NP39</t>
-        </is>
-      </c>
-      <c r="E68" s="138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F68" s="138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G68" s="138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H68" s="138" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="O68" s="140" t="n"/>
-      <c r="Q68" s="140" t="n"/>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="68" ht="43.15" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B68" t="n">
         <v>3058</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Hunkemoller</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>NP15</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>NL01</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>Sterkenburg 3-5
 1358 CG Almere
 Netherlands</t>
         </is>
       </c>
+      <c r="O68" s="4" t="n"/>
+      <c r="Q68" s="4" t="n"/>
+    </row>
+    <row r="69" ht="14.45" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3059</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NP16</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NL02</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
       <c r="O69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="14.45" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>DG Beauty</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NP16</t>
+          <t>NP17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NL02</t>
+          <t>IT01</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5026,138 +5045,138 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="14.45" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DG Beauty</t>
+          <t>Oh Polly</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NP17</t>
+          <t>NP18</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PR6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>IT01</t>
+          <t>PL01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>bh10</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Poznan, PL</t>
         </is>
       </c>
       <c r="O71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="72" ht="43.15" customHeight="1">
       <c r="B72" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oh Polly</t>
+          <t>Nodor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NP18</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>PR6</t>
+          <t>NP45</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PL01</t>
+          <t>DJ1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Poznan, PL</t>
-        </is>
-      </c>
-      <c r="O72" s="4" t="n"/>
-      <c r="Q72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="B73" t="n">
-        <v>3063</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Nodor</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NP45</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>DJ1</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>2353 US-130
 Dayton, NJ 08810
 USA</t>
         </is>
       </c>
+      <c r="O72" s="4" t="n"/>
+      <c r="Q72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="14.45" customHeight="1">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3064 &amp; 3070</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Affinity Petcare</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NP19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>FR01</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
       <c r="O73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="57.6" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>3064 &amp; 3070</t>
-        </is>
+      <c r="B74" t="n">
+        <v>3065</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Affinity Petcare</t>
+          <t>Columbia Sportswear Distribution SaS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NP19</t>
+          <t>NP20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FR01</t>
+          <t>FR02</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5165,199 +5184,209 @@
           <t>bh10</t>
         </is>
       </c>
-      <c r="O74" s="4" t="n"/>
-      <c r="Q74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>3065</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Columbia Sportswear Distribution SaS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NP20</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>FR02</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>1542 Avenue des Deux Vallees Parc d'Activites Actipole de l'A25
 9954 Raillencourt Sainte Olle
 France</t>
         </is>
       </c>
-      <c r="O75" s="4" t="n"/>
-      <c r="Q75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" t="inlineStr">
+      <c r="O74" s="4" t="n"/>
+      <c r="Q74" s="4" t="n"/>
+    </row>
+    <row r="75" ht="43.15" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B75" t="n">
         <v>3066</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>GXO (Multi Tenant)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>NP21</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>IT02</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>Via della Libertà, 215
 28043 Bellinzago Novarese NO
 Italy</t>
         </is>
       </c>
+      <c r="O75" s="4" t="n"/>
+      <c r="Q75" s="4" t="n"/>
+    </row>
+    <row r="76" ht="28.9" customHeight="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3067</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Nodor</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NP3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PR1A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DN1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2023.1.0.37.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2023.1.0.37</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>bh10-003-euw</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-passenger-les</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>bh10-002-euw</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
+        </is>
+      </c>
       <c r="O76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
     </row>
-    <row r="77" ht="30" customHeight="1">
+    <row r="77" ht="43.15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nodor</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NP3</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>PR1</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>PR1A</t>
+          <t>NP42</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DN1</t>
+          <t>WOH</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2023.1.0.37.0</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>2023.1.0.37</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>bh10-003-euw</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-passenger-les</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>bh10-002-euw</t>
+          <t>be40</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
-        </is>
-      </c>
-      <c r="O77" s="4" t="n"/>
-      <c r="Q77" s="4" t="n"/>
-    </row>
-    <row r="78" ht="45" customHeight="1">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>3068</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Vuori</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NP42</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>WOH</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>202 Park West Dr
 West Jefferson, OH
 USA</t>
         </is>
       </c>
+      <c r="O77" s="4" t="n"/>
+      <c r="Q77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="14.45" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3069</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Allied Air</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NP46</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PR28</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>PR28A</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="43.15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
           <t>US</t>
@@ -5373,22 +5402,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NP46</t>
+          <t>BY Case 05787158</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PR28</t>
+          <t>BY Case 05787162</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PR28A</t>
+          <t>BY Case 05787162A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>KAI</t>
+          <t>KAO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5396,2072 +5425,2102 @@
           <t>be40</t>
         </is>
       </c>
-      <c r="O79" s="4" t="n"/>
-      <c r="Q79" s="4" t="n"/>
-    </row>
-    <row r="80" ht="45.75" customHeight="1">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>3069</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Allied Air</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BY Case 05787158</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>BY Case 05787162</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>BY Case 05787162A</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>KAO</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>319 Millennium Drive
 Orangeburg, SC 29115
 USA</t>
         </is>
       </c>
+      <c r="O79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="14.45" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3071</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>req</t>
+        </is>
+      </c>
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="14.45" customHeight="1">
       <c r="B81" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="14.45" customHeight="1">
       <c r="B82" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="14.45" customHeight="1">
       <c r="B83" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="14.45" customHeight="1">
       <c r="B84" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="14.45" customHeight="1">
       <c r="B85" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="14.45" customHeight="1">
       <c r="B86" t="n">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="14.45" customHeight="1">
       <c r="B87" t="n">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" ht="14.45" customHeight="1">
       <c r="B88" t="n">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="14.45" customHeight="1">
       <c r="B89" t="n">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="14.45" customHeight="1">
       <c r="B90" t="n">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" ht="14.45" customHeight="1">
       <c r="B91" t="n">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" ht="14.45" customHeight="1">
       <c r="B92" t="n">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" ht="14.45" customHeight="1">
       <c r="B93" t="n">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="14.45" customHeight="1">
       <c r="B94" t="n">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="14.45" customHeight="1">
       <c r="B95" t="n">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="14.45" customHeight="1">
       <c r="B96" t="n">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="14.45" customHeight="1">
       <c r="B97" t="n">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" ht="14.45" customHeight="1">
       <c r="B98" t="n">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="14.45" customHeight="1">
       <c r="B99" t="n">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="14.45" customHeight="1">
       <c r="B100" t="n">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" ht="14.45" customHeight="1">
       <c r="B101" t="n">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="14.45" customHeight="1">
       <c r="B102" t="n">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="14.45" customHeight="1">
       <c r="B103" t="n">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="14.45" customHeight="1">
       <c r="B104" t="n">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="14.45" customHeight="1">
       <c r="B105" t="n">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="14.45" customHeight="1">
       <c r="B106" t="n">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="14.45" customHeight="1">
       <c r="B107" t="n">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="14.45" customHeight="1">
       <c r="B108" t="n">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="14.45" customHeight="1">
       <c r="B109" t="n">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="14.45" customHeight="1">
       <c r="B110" t="n">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="14.45" customHeight="1">
       <c r="B111" t="n">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="14.45" customHeight="1">
       <c r="B112" t="n">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="14.45" customHeight="1">
       <c r="B113" t="n">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" ht="14.45" customHeight="1">
       <c r="B114" t="n">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" ht="14.45" customHeight="1">
       <c r="B115" t="n">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" ht="14.45" customHeight="1">
       <c r="B116" t="n">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" ht="14.45" customHeight="1">
       <c r="B117" t="n">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" ht="14.45" customHeight="1">
       <c r="B118" t="n">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="14.45" customHeight="1">
       <c r="B119" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="14.45" customHeight="1">
       <c r="B120" t="n">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="14.45" customHeight="1">
       <c r="B121" t="n">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" ht="14.45" customHeight="1">
       <c r="B122" t="n">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="14.45" customHeight="1">
       <c r="B123" t="n">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="14.45" customHeight="1">
       <c r="B124" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="14.45" customHeight="1">
       <c r="B125" t="n">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="14.45" customHeight="1">
       <c r="B126" t="n">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" ht="14.45" customHeight="1">
       <c r="B127" t="n">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" ht="14.45" customHeight="1">
       <c r="B128" t="n">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" ht="14.45" customHeight="1">
       <c r="B129" t="n">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" ht="14.45" customHeight="1">
       <c r="B130" t="n">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="14.45" customHeight="1">
       <c r="B131" t="n">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="14.45" customHeight="1">
       <c r="B132" t="n">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" ht="14.45" customHeight="1">
       <c r="B133" t="n">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" ht="14.45" customHeight="1">
       <c r="B134" t="n">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" ht="14.45" customHeight="1">
       <c r="B135" t="n">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="14.45" customHeight="1">
       <c r="B136" t="n">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="14.45" customHeight="1">
       <c r="B137" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="14.45" customHeight="1">
       <c r="B138" t="n">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="14.45" customHeight="1">
       <c r="B139" t="n">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="14.45" customHeight="1">
       <c r="B140" t="n">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" ht="14.45" customHeight="1">
       <c r="B141" t="n">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" ht="14.45" customHeight="1">
       <c r="B142" t="n">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="14.45" customHeight="1">
       <c r="B143" t="n">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="14.45" customHeight="1">
       <c r="B144" t="n">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="14.45" customHeight="1">
       <c r="B145" t="n">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="14.45" customHeight="1">
       <c r="B146" t="n">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="14.45" customHeight="1">
       <c r="B147" t="n">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" ht="14.45" customHeight="1">
       <c r="B148" t="n">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" ht="14.45" customHeight="1">
       <c r="B149" t="n">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="14.45" customHeight="1">
       <c r="B150" t="n">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" ht="14.45" customHeight="1">
       <c r="B151" t="n">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="14.45" customHeight="1">
       <c r="B152" t="n">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="14.45" customHeight="1">
       <c r="B153" t="n">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" ht="14.45" customHeight="1">
       <c r="B154" t="n">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" ht="14.45" customHeight="1">
       <c r="B155" t="n">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="14.45" customHeight="1">
       <c r="B156" t="n">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" ht="14.45" customHeight="1">
       <c r="B157" t="n">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" ht="14.45" customHeight="1">
       <c r="B158" t="n">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" ht="14.45" customHeight="1">
       <c r="B159" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" ht="14.45" customHeight="1">
       <c r="B160" t="n">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" ht="14.45" customHeight="1">
       <c r="B161" t="n">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" ht="14.45" customHeight="1">
       <c r="B162" t="n">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" ht="14.45" customHeight="1">
       <c r="B163" t="n">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" ht="14.45" customHeight="1">
       <c r="B164" t="n">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" ht="14.45" customHeight="1">
       <c r="B165" t="n">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" ht="14.45" customHeight="1">
       <c r="B166" t="n">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" ht="14.45" customHeight="1">
       <c r="B167" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" ht="14.45" customHeight="1">
       <c r="B168" t="n">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" ht="14.45" customHeight="1">
       <c r="B169" t="n">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" ht="14.45" customHeight="1">
       <c r="B170" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" ht="14.45" customHeight="1">
       <c r="B171" t="n">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" ht="14.45" customHeight="1">
       <c r="B172" t="n">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" ht="14.45" customHeight="1">
       <c r="B173" t="n">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" ht="14.45" customHeight="1">
       <c r="B174" t="n">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" ht="14.45" customHeight="1">
       <c r="B175" t="n">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" ht="14.45" customHeight="1">
       <c r="B176" t="n">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" ht="14.45" customHeight="1">
       <c r="B177" t="n">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" ht="14.45" customHeight="1">
       <c r="B178" t="n">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" ht="14.45" customHeight="1">
       <c r="B179" t="n">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" ht="14.45" customHeight="1">
       <c r="B180" t="n">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" ht="14.45" customHeight="1">
       <c r="B181" t="n">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" ht="14.45" customHeight="1">
       <c r="B182" t="n">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="14.45" customHeight="1">
       <c r="B183" t="n">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" ht="14.45" customHeight="1">
       <c r="B184" t="n">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" ht="14.45" customHeight="1">
       <c r="B185" t="n">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" ht="14.45" customHeight="1">
       <c r="B186" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" ht="14.45" customHeight="1">
       <c r="B187" t="n">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" ht="14.45" customHeight="1">
       <c r="B188" t="n">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" ht="14.45" customHeight="1">
       <c r="B189" t="n">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" ht="14.45" customHeight="1">
       <c r="B190" t="n">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" ht="14.45" customHeight="1">
       <c r="B191" t="n">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" ht="14.45" customHeight="1">
       <c r="B192" t="n">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" ht="14.45" customHeight="1">
       <c r="B193" t="n">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" ht="14.45" customHeight="1">
       <c r="B194" t="n">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" ht="14.45" customHeight="1">
       <c r="B195" t="n">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" ht="14.45" customHeight="1">
       <c r="B196" t="n">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" ht="14.45" customHeight="1">
       <c r="B197" t="n">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" ht="14.45" customHeight="1">
       <c r="B198" t="n">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" ht="14.45" customHeight="1">
       <c r="B199" t="n">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" ht="14.45" customHeight="1">
       <c r="B200" t="n">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" ht="14.45" customHeight="1">
       <c r="B201" t="n">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" ht="14.45" customHeight="1">
       <c r="B202" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" ht="14.45" customHeight="1">
       <c r="B203" t="n">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" ht="14.45" customHeight="1">
       <c r="B204" t="n">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="14.45" customHeight="1">
       <c r="B205" t="n">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" ht="14.45" customHeight="1">
       <c r="B206" t="n">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" ht="14.45" customHeight="1">
       <c r="B207" t="n">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" ht="14.45" customHeight="1">
       <c r="B208" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" ht="14.45" customHeight="1">
       <c r="B209" t="n">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" ht="14.45" customHeight="1">
       <c r="B210" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" ht="14.45" customHeight="1">
       <c r="B211" t="n">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" ht="14.45" customHeight="1">
       <c r="B212" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" ht="14.45" customHeight="1">
       <c r="B213" t="n">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" ht="14.45" customHeight="1">
       <c r="B214" t="n">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" ht="14.45" customHeight="1">
       <c r="B215" t="n">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" ht="14.45" customHeight="1">
       <c r="B216" t="n">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" ht="14.45" customHeight="1">
       <c r="B217" t="n">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" ht="14.45" customHeight="1">
       <c r="B218" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" ht="14.45" customHeight="1">
       <c r="B219" t="n">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" ht="14.45" customHeight="1">
       <c r="B220" t="n">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="14.45" customHeight="1">
       <c r="B221" t="n">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" ht="14.45" customHeight="1">
       <c r="B222" t="n">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" ht="14.45" customHeight="1">
       <c r="B223" t="n">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" ht="14.45" customHeight="1">
       <c r="B224" t="n">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" ht="14.45" customHeight="1">
       <c r="B225" t="n">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" ht="14.45" customHeight="1">
       <c r="B226" t="n">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" ht="14.45" customHeight="1">
       <c r="B227" t="n">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" ht="14.45" customHeight="1">
       <c r="B228" t="n">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" ht="14.45" customHeight="1">
       <c r="B229" t="n">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" ht="14.45" customHeight="1">
       <c r="B230" t="n">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" ht="14.45" customHeight="1">
       <c r="B231" t="n">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" ht="14.45" customHeight="1">
       <c r="B232" t="n">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" ht="14.45" customHeight="1">
       <c r="B233" t="n">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" ht="14.45" customHeight="1">
       <c r="B234" t="n">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" ht="14.45" customHeight="1">
       <c r="B235" t="n">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236">
+    <row r="236" ht="14.45" customHeight="1">
       <c r="B236" t="n">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" ht="14.45" customHeight="1">
       <c r="B237" t="n">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" ht="14.45" customHeight="1">
       <c r="B238" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" ht="14.45" customHeight="1">
       <c r="B239" t="n">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240">
+    <row r="240" ht="14.45" customHeight="1">
       <c r="B240" t="n">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" ht="14.45" customHeight="1">
       <c r="B241" t="n">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242">
+    <row r="242" ht="14.45" customHeight="1">
       <c r="B242" t="n">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" ht="14.45" customHeight="1">
       <c r="B243" t="n">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" ht="14.45" customHeight="1">
       <c r="B244" t="n">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" ht="14.45" customHeight="1">
       <c r="B245" t="n">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" ht="14.45" customHeight="1">
       <c r="B246" t="n">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" ht="14.45" customHeight="1">
       <c r="B247" t="n">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" ht="14.45" customHeight="1">
       <c r="B248" t="n">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" ht="14.45" customHeight="1">
       <c r="B249" t="n">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" ht="14.45" customHeight="1">
       <c r="B250" t="n">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" ht="14.45" customHeight="1">
       <c r="B251" t="n">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" ht="14.45" customHeight="1">
       <c r="B252" t="n">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" ht="14.45" customHeight="1">
       <c r="B253" t="n">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254">
+    <row r="254" ht="14.45" customHeight="1">
       <c r="B254" t="n">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255">
+    <row r="255" ht="14.45" customHeight="1">
       <c r="B255" t="n">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256">
+    <row r="256" ht="14.45" customHeight="1">
       <c r="B256" t="n">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257">
+    <row r="257" ht="14.45" customHeight="1">
       <c r="B257" t="n">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258">
+    <row r="258" ht="14.45" customHeight="1">
       <c r="B258" t="n">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259">
+    <row r="259" ht="14.45" customHeight="1">
       <c r="B259" t="n">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260">
+    <row r="260" ht="14.45" customHeight="1">
       <c r="B260" t="n">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261">
+    <row r="261" ht="14.45" customHeight="1">
       <c r="B261" t="n">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262">
+    <row r="262" ht="14.45" customHeight="1">
       <c r="B262" t="n">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263">
+    <row r="263" ht="14.45" customHeight="1">
       <c r="B263" t="n">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264">
+    <row r="264" ht="14.45" customHeight="1">
       <c r="B264" t="n">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265">
+    <row r="265" ht="14.45" customHeight="1">
       <c r="B265" t="n">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266">
+    <row r="266" ht="14.45" customHeight="1">
       <c r="B266" t="n">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267">
+    <row r="267" ht="14.45" customHeight="1">
       <c r="B267" t="n">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268">
+    <row r="268" ht="14.45" customHeight="1">
       <c r="B268" t="n">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269">
+    <row r="269" ht="14.45" customHeight="1">
       <c r="B269" t="n">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270">
+    <row r="270" ht="14.45" customHeight="1">
       <c r="B270" t="n">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271">
+    <row r="271" ht="14.45" customHeight="1">
       <c r="B271" t="n">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272">
+    <row r="272" ht="14.45" customHeight="1">
       <c r="B272" t="n">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273">
+    <row r="273" ht="14.45" customHeight="1">
       <c r="B273" t="n">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274">
+    <row r="274" ht="14.45" customHeight="1">
       <c r="B274" t="n">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275">
+    <row r="275" ht="14.45" customHeight="1">
       <c r="B275" t="n">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276">
+    <row r="276" ht="14.45" customHeight="1">
       <c r="B276" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277">
+    <row r="277" ht="14.45" customHeight="1">
       <c r="B277" t="n">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278">
+    <row r="278" ht="14.45" customHeight="1">
       <c r="B278" t="n">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279">
+    <row r="279" ht="14.45" customHeight="1">
       <c r="B279" t="n">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280">
+    <row r="280" ht="14.45" customHeight="1">
       <c r="B280" t="n">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281">
+    <row r="281" ht="14.45" customHeight="1">
       <c r="B281" t="n">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282">
+    <row r="282" ht="14.45" customHeight="1">
       <c r="B282" t="n">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" ht="14.45" customHeight="1">
       <c r="B283" t="n">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284">
+    <row r="284" ht="14.45" customHeight="1">
       <c r="B284" t="n">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285">
+    <row r="285" ht="14.45" customHeight="1">
       <c r="B285" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286">
+    <row r="286" ht="14.45" customHeight="1">
       <c r="B286" t="n">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287">
+    <row r="287" ht="14.45" customHeight="1">
       <c r="B287" t="n">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" ht="14.45" customHeight="1">
       <c r="B288" t="n">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" ht="14.45" customHeight="1">
       <c r="B289" t="n">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" ht="14.45" customHeight="1">
       <c r="B290" t="n">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291">
+    <row r="291" ht="14.45" customHeight="1">
       <c r="B291" t="n">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292">
+    <row r="292" ht="14.45" customHeight="1">
       <c r="B292" t="n">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293">
+    <row r="293" ht="14.45" customHeight="1">
       <c r="B293" t="n">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" ht="14.45" customHeight="1">
       <c r="B294" t="n">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295">
+    <row r="295" ht="14.45" customHeight="1">
       <c r="B295" t="n">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296">
+    <row r="296" ht="14.45" customHeight="1">
       <c r="B296" t="n">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297">
+    <row r="297" ht="14.45" customHeight="1">
       <c r="B297" t="n">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298">
+    <row r="298" ht="14.45" customHeight="1">
       <c r="B298" t="n">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299">
+    <row r="299" ht="14.45" customHeight="1">
       <c r="B299" t="n">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300">
+    <row r="300" ht="14.45" customHeight="1">
       <c r="B300" t="n">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301">
+    <row r="301" ht="14.45" customHeight="1">
       <c r="B301" t="n">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302">
+    <row r="302" ht="14.45" customHeight="1">
       <c r="B302" t="n">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303">
+    <row r="303" ht="14.45" customHeight="1">
       <c r="B303" t="n">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" ht="14.45" customHeight="1">
       <c r="B304" t="n">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305">
+    <row r="305" ht="14.45" customHeight="1">
       <c r="B305" t="n">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" ht="14.45" customHeight="1">
       <c r="B306" t="n">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" ht="14.45" customHeight="1">
       <c r="B307" t="n">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308">
+    <row r="308" ht="14.45" customHeight="1">
       <c r="B308" t="n">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" ht="14.45" customHeight="1">
       <c r="B309" t="n">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310">
+    <row r="310" ht="14.45" customHeight="1">
       <c r="B310" t="n">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311">
+    <row r="311" ht="14.45" customHeight="1">
       <c r="B311" t="n">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312">
+    <row r="312" ht="14.45" customHeight="1">
       <c r="B312" t="n">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313">
+    <row r="313" ht="14.45" customHeight="1">
       <c r="B313" t="n">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314">
+    <row r="314" ht="14.45" customHeight="1">
       <c r="B314" t="n">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315">
+    <row r="315" ht="14.45" customHeight="1">
       <c r="B315" t="n">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316">
+    <row r="316" ht="14.45" customHeight="1">
       <c r="B316" t="n">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317">
+    <row r="317" ht="14.45" customHeight="1">
       <c r="B317" t="n">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318">
+    <row r="318" ht="14.45" customHeight="1">
       <c r="B318" t="n">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319">
+    <row r="319" ht="14.45" customHeight="1">
       <c r="B319" t="n">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320">
+    <row r="320" ht="14.45" customHeight="1">
       <c r="B320" t="n">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321">
+    <row r="321" ht="14.45" customHeight="1">
       <c r="B321" t="n">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322">
+    <row r="322" ht="14.45" customHeight="1">
       <c r="B322" t="n">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323">
+    <row r="323" ht="14.45" customHeight="1">
       <c r="B323" t="n">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324">
+    <row r="324" ht="14.45" customHeight="1">
       <c r="B324" t="n">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325">
+    <row r="325" ht="14.45" customHeight="1">
       <c r="B325" t="n">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326">
+    <row r="326" ht="14.45" customHeight="1">
       <c r="B326" t="n">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327">
+    <row r="327" ht="14.45" customHeight="1">
       <c r="B327" t="n">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328">
+    <row r="328" ht="14.45" customHeight="1">
       <c r="B328" t="n">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329">
+    <row r="329" ht="14.45" customHeight="1">
       <c r="B329" t="n">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330">
+    <row r="330" ht="14.45" customHeight="1">
       <c r="B330" t="n">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331">
+    <row r="331" ht="14.45" customHeight="1">
       <c r="B331" t="n">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332">
+    <row r="332" ht="14.45" customHeight="1">
       <c r="B332" t="n">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333">
+    <row r="333" ht="14.45" customHeight="1">
       <c r="B333" t="n">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334">
+    <row r="334" ht="14.45" customHeight="1">
       <c r="B334" t="n">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335">
+    <row r="335" ht="14.45" customHeight="1">
       <c r="B335" t="n">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336">
+    <row r="336" ht="14.45" customHeight="1">
       <c r="B336" t="n">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337">
+    <row r="337" ht="14.45" customHeight="1">
       <c r="B337" t="n">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338">
+    <row r="338" ht="14.45" customHeight="1">
       <c r="B338" t="n">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339">
+    <row r="339" ht="14.45" customHeight="1">
       <c r="B339" t="n">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340">
+    <row r="340" ht="14.45" customHeight="1">
       <c r="B340" t="n">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341">
+    <row r="341" ht="14.45" customHeight="1">
       <c r="B341" t="n">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342">
+    <row r="342" ht="14.45" customHeight="1">
       <c r="B342" t="n">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343">
+    <row r="343" ht="14.45" customHeight="1">
       <c r="B343" t="n">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344">
+    <row r="344" ht="14.45" customHeight="1">
       <c r="B344" t="n">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345">
+    <row r="345" ht="14.45" customHeight="1">
       <c r="B345" t="n">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346">
+    <row r="346" ht="14.45" customHeight="1">
       <c r="B346" t="n">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347">
+    <row r="347" ht="14.45" customHeight="1">
       <c r="B347" t="n">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348">
+    <row r="348" ht="14.45" customHeight="1">
       <c r="B348" t="n">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349">
+    <row r="349" ht="14.45" customHeight="1">
       <c r="B349" t="n">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350">
+    <row r="350" ht="14.45" customHeight="1">
       <c r="B350" t="n">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351">
+    <row r="351" ht="14.45" customHeight="1">
       <c r="B351" t="n">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352">
+    <row r="352" ht="14.45" customHeight="1">
       <c r="B352" t="n">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353">
+    <row r="353" ht="14.45" customHeight="1">
       <c r="B353" t="n">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354">
+    <row r="354" ht="14.45" customHeight="1">
       <c r="B354" t="n">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355">
+    <row r="355" ht="14.45" customHeight="1">
       <c r="B355" t="n">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356">
+    <row r="356" ht="14.45" customHeight="1">
       <c r="B356" t="n">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" ht="14.45" customHeight="1">
       <c r="B357" t="n">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358">
+    <row r="358" ht="14.45" customHeight="1">
       <c r="B358" t="n">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359">
+    <row r="359" ht="14.45" customHeight="1">
       <c r="B359" t="n">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360">
+    <row r="360" ht="14.45" customHeight="1">
       <c r="B360" t="n">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361">
+    <row r="361" ht="14.45" customHeight="1">
       <c r="B361" t="n">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362">
+    <row r="362" ht="14.45" customHeight="1">
       <c r="B362" t="n">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363">
+    <row r="363" ht="14.45" customHeight="1">
       <c r="B363" t="n">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364">
+    <row r="364" ht="14.45" customHeight="1">
       <c r="B364" t="n">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365">
+    <row r="365" ht="14.45" customHeight="1">
       <c r="B365" t="n">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366">
+    <row r="366" ht="14.45" customHeight="1">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B366" t="n">
-        <v>3356</v>
+        <v>3357</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Unilever FOOD</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367">
+    <row r="367" ht="14.45" customHeight="1">
       <c r="A367" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Unilever FOOD</t>
+          <t>Unilever HOME CARE</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -7507,18 +7566,18 @@
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368">
+    <row r="368" ht="14.45" customHeight="1">
       <c r="A368" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unilever HOME CARE</t>
+          <t>Unilever Personal Care</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -7564,1144 +7623,1099 @@
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="369" ht="14.45" customHeight="1">
       <c r="B369" t="n">
-        <v>3359</v>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Unilever Personal Care</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>NP8</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>FEG</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>bh10-00j-euw</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
+        <v>3360</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370">
+    <row r="370" ht="14.45" customHeight="1">
       <c r="B370" t="n">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371">
+    <row r="371" ht="14.45" customHeight="1">
       <c r="B371" t="n">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372">
+    <row r="372" ht="14.45" customHeight="1">
       <c r="B372" t="n">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373">
+    <row r="373" ht="14.45" customHeight="1">
       <c r="B373" t="n">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374">
+    <row r="374" ht="14.45" customHeight="1">
       <c r="B374" t="n">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375">
+    <row r="375" ht="14.45" customHeight="1">
       <c r="B375" t="n">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376">
+    <row r="376" ht="14.45" customHeight="1">
       <c r="B376" t="n">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377">
+    <row r="377" ht="14.45" customHeight="1">
       <c r="B377" t="n">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" ht="14.45" customHeight="1">
       <c r="B378" t="n">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379">
+    <row r="379" ht="14.45" customHeight="1">
       <c r="B379" t="n">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380">
+    <row r="380" ht="14.45" customHeight="1">
       <c r="B380" t="n">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381">
+    <row r="381" ht="14.45" customHeight="1">
       <c r="B381" t="n">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382">
+    <row r="382" ht="14.45" customHeight="1">
       <c r="B382" t="n">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383">
+    <row r="383" ht="14.45" customHeight="1">
       <c r="B383" t="n">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384">
+    <row r="384" ht="14.45" customHeight="1">
       <c r="B384" t="n">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385">
+    <row r="385" ht="14.45" customHeight="1">
       <c r="B385" t="n">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386">
+    <row r="386" ht="14.45" customHeight="1">
       <c r="B386" t="n">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" ht="14.45" customHeight="1">
       <c r="B387" t="n">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388">
+    <row r="388" ht="14.45" customHeight="1">
       <c r="B388" t="n">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389">
+    <row r="389" ht="14.45" customHeight="1">
       <c r="B389" t="n">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390">
+    <row r="390" ht="14.45" customHeight="1">
       <c r="B390" t="n">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391">
+    <row r="391" ht="14.45" customHeight="1">
       <c r="B391" t="n">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392">
+    <row r="392" ht="14.45" customHeight="1">
       <c r="B392" t="n">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393">
+    <row r="393" ht="14.45" customHeight="1">
       <c r="B393" t="n">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394">
+    <row r="394" ht="14.45" customHeight="1">
       <c r="B394" t="n">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395">
+    <row r="395" ht="14.45" customHeight="1">
       <c r="B395" t="n">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396">
+    <row r="396" ht="14.45" customHeight="1">
       <c r="B396" t="n">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397">
+    <row r="397" ht="14.45" customHeight="1">
       <c r="B397" t="n">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398">
+    <row r="398" ht="14.45" customHeight="1">
       <c r="B398" t="n">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399">
+    <row r="399" ht="14.45" customHeight="1">
       <c r="B399" t="n">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400">
+    <row r="400" ht="14.45" customHeight="1">
       <c r="B400" t="n">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401">
+    <row r="401" ht="14.45" customHeight="1">
       <c r="B401" t="n">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402">
+    <row r="402" ht="14.45" customHeight="1">
       <c r="B402" t="n">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403">
+    <row r="403" ht="14.45" customHeight="1">
       <c r="B403" t="n">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404">
+    <row r="404" ht="14.45" customHeight="1">
       <c r="B404" t="n">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405">
+    <row r="405" ht="14.45" customHeight="1">
       <c r="B405" t="n">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406">
+    <row r="406" ht="14.45" customHeight="1">
       <c r="B406" t="n">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407">
+    <row r="407" ht="14.45" customHeight="1">
       <c r="B407" t="n">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408">
+    <row r="408" ht="14.45" customHeight="1">
       <c r="B408" t="n">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409">
+    <row r="409" ht="14.45" customHeight="1">
       <c r="B409" t="n">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410">
+    <row r="410" ht="14.45" customHeight="1">
       <c r="B410" t="n">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411">
+    <row r="411" ht="14.45" customHeight="1">
       <c r="B411" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412">
+    <row r="412" ht="14.45" customHeight="1">
       <c r="B412" t="n">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413">
+    <row r="413" ht="14.45" customHeight="1">
       <c r="B413" t="n">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414">
+    <row r="414" ht="14.45" customHeight="1">
       <c r="B414" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415">
+    <row r="415" ht="14.45" customHeight="1">
       <c r="B415" t="n">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416">
+    <row r="416" ht="14.45" customHeight="1">
       <c r="B416" t="n">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417">
+    <row r="417" ht="14.45" customHeight="1">
       <c r="B417" t="n">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418">
+    <row r="418" ht="14.45" customHeight="1">
       <c r="B418" t="n">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419">
+    <row r="419" ht="14.45" customHeight="1">
       <c r="B419" t="n">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420">
+    <row r="420" ht="14.45" customHeight="1">
       <c r="B420" t="n">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421">
+    <row r="421" ht="14.45" customHeight="1">
       <c r="B421" t="n">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422">
+    <row r="422" ht="14.45" customHeight="1">
       <c r="B422" t="n">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423">
+    <row r="423" ht="14.45" customHeight="1">
       <c r="B423" t="n">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424">
+    <row r="424" ht="14.45" customHeight="1">
       <c r="B424" t="n">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425">
+    <row r="425" ht="14.45" customHeight="1">
       <c r="B425" t="n">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426">
+    <row r="426" ht="14.45" customHeight="1">
       <c r="B426" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427">
+    <row r="427" ht="14.45" customHeight="1">
       <c r="B427" t="n">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428">
+    <row r="428" ht="14.45" customHeight="1">
       <c r="B428" t="n">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429">
+    <row r="429" ht="14.45" customHeight="1">
       <c r="B429" t="n">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430">
+    <row r="430" ht="14.45" customHeight="1">
       <c r="B430" t="n">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431">
+    <row r="431" ht="14.45" customHeight="1">
       <c r="B431" t="n">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432">
+    <row r="432" ht="14.45" customHeight="1">
       <c r="B432" t="n">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433">
+    <row r="433" ht="14.45" customHeight="1">
       <c r="B433" t="n">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434">
+    <row r="434" ht="14.45" customHeight="1">
       <c r="B434" t="n">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435">
+    <row r="435" ht="14.45" customHeight="1">
       <c r="B435" t="n">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436">
+    <row r="436" ht="14.45" customHeight="1">
       <c r="B436" t="n">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" ht="14.45" customHeight="1">
       <c r="B437" t="n">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438">
+    <row r="438" ht="14.45" customHeight="1">
       <c r="B438" t="n">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439">
+    <row r="439" ht="14.45" customHeight="1">
       <c r="B439" t="n">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440">
+    <row r="440" ht="14.45" customHeight="1">
       <c r="B440" t="n">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441">
+    <row r="441" ht="14.45" customHeight="1">
       <c r="B441" t="n">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442">
+    <row r="442" ht="14.45" customHeight="1">
       <c r="B442" t="n">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443">
+    <row r="443" ht="14.45" customHeight="1">
       <c r="B443" t="n">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444">
+    <row r="444" ht="14.45" customHeight="1">
       <c r="B444" t="n">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445">
+    <row r="445" ht="14.45" customHeight="1">
       <c r="B445" t="n">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446">
+    <row r="446" ht="14.45" customHeight="1">
       <c r="B446" t="n">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447">
+    <row r="447" ht="14.45" customHeight="1">
       <c r="B447" t="n">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448">
+    <row r="448" ht="14.45" customHeight="1">
       <c r="B448" t="n">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449">
+    <row r="449" ht="14.45" customHeight="1">
       <c r="B449" t="n">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450">
+    <row r="450" ht="14.45" customHeight="1">
       <c r="B450" t="n">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451">
+    <row r="451" ht="14.45" customHeight="1">
       <c r="B451" t="n">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452">
+    <row r="452" ht="14.45" customHeight="1">
       <c r="B452" t="n">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453">
+    <row r="453" ht="14.45" customHeight="1">
       <c r="B453" t="n">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454">
+    <row r="454" ht="14.45" customHeight="1">
       <c r="B454" t="n">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455">
+    <row r="455" ht="14.45" customHeight="1">
       <c r="B455" t="n">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456">
+    <row r="456" ht="14.45" customHeight="1">
       <c r="B456" t="n">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457">
+    <row r="457" ht="14.45" customHeight="1">
       <c r="B457" t="n">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458">
+    <row r="458" ht="14.45" customHeight="1">
       <c r="B458" t="n">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459">
+    <row r="459" ht="14.45" customHeight="1">
       <c r="B459" t="n">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460">
+    <row r="460" ht="14.45" customHeight="1">
       <c r="B460" t="n">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461">
+    <row r="461" ht="14.45" customHeight="1">
       <c r="B461" t="n">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462">
+    <row r="462" ht="14.45" customHeight="1">
       <c r="B462" t="n">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463">
+    <row r="463" ht="14.45" customHeight="1">
       <c r="B463" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464">
+    <row r="464" ht="14.45" customHeight="1">
       <c r="B464" t="n">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465">
+    <row r="465" ht="14.45" customHeight="1">
       <c r="B465" t="n">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466">
+    <row r="466" ht="14.45" customHeight="1">
       <c r="B466" t="n">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467">
+    <row r="467" ht="14.45" customHeight="1">
       <c r="B467" t="n">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468">
+    <row r="468" ht="14.45" customHeight="1">
       <c r="B468" t="n">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469">
+    <row r="469" ht="14.45" customHeight="1">
       <c r="B469" t="n">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470">
+    <row r="470" ht="14.45" customHeight="1">
       <c r="B470" t="n">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471">
+    <row r="471" ht="14.45" customHeight="1">
       <c r="B471" t="n">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472">
+    <row r="472" ht="14.45" customHeight="1">
       <c r="B472" t="n">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473">
+    <row r="473" ht="14.45" customHeight="1">
       <c r="B473" t="n">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474">
+    <row r="474" ht="14.45" customHeight="1">
       <c r="B474" t="n">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475">
+    <row r="475" ht="14.45" customHeight="1">
       <c r="B475" t="n">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476">
+    <row r="476" ht="14.45" customHeight="1">
       <c r="B476" t="n">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477">
+    <row r="477" ht="14.45" customHeight="1">
       <c r="B477" t="n">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478">
+    <row r="478" ht="14.45" customHeight="1">
       <c r="B478" t="n">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479">
+    <row r="479" ht="14.45" customHeight="1">
       <c r="B479" t="n">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480">
+    <row r="480" ht="14.45" customHeight="1">
       <c r="B480" t="n">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481">
+    <row r="481" ht="14.45" customHeight="1">
       <c r="B481" t="n">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482">
+    <row r="482" ht="14.45" customHeight="1">
       <c r="B482" t="n">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483">
+    <row r="483" ht="14.45" customHeight="1">
       <c r="B483" t="n">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484">
+    <row r="484" ht="14.45" customHeight="1">
       <c r="B484" t="n">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" ht="14.45" customHeight="1">
       <c r="B485" t="n">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" ht="14.45" customHeight="1">
       <c r="B486" t="n">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487">
+    <row r="487" ht="14.45" customHeight="1">
       <c r="B487" t="n">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488">
+    <row r="488" ht="14.45" customHeight="1">
       <c r="B488" t="n">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489">
+    <row r="489" ht="14.45" customHeight="1">
       <c r="B489" t="n">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490">
+    <row r="490" ht="14.45" customHeight="1">
       <c r="B490" t="n">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491">
+    <row r="491" ht="14.45" customHeight="1">
       <c r="B491" t="n">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492">
+    <row r="492" ht="14.45" customHeight="1">
       <c r="B492" t="n">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493">
+    <row r="493" ht="14.45" customHeight="1">
       <c r="B493" t="n">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494">
+    <row r="494" ht="14.45" customHeight="1">
       <c r="B494" t="n">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495">
+    <row r="495" ht="14.45" customHeight="1">
       <c r="B495" t="n">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496">
+    <row r="496" ht="14.45" customHeight="1">
       <c r="B496" t="n">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497">
+    <row r="497" ht="14.45" customHeight="1">
       <c r="B497" t="n">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" ht="14.45" customHeight="1">
       <c r="B498" t="n">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" ht="14.45" customHeight="1">
       <c r="B499" t="n">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500">
+    <row r="500" ht="14.45" customHeight="1">
       <c r="B500" t="n">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501">
+    <row r="501" ht="14.45" customHeight="1">
       <c r="B501" t="n">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502">
+    <row r="502" ht="14.45" customHeight="1">
       <c r="B502" t="n">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503">
+    <row r="503" ht="14.45" customHeight="1">
       <c r="B503" t="n">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504">
+    <row r="504" ht="14.45" customHeight="1">
       <c r="B504" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505">
+    <row r="505" ht="14.45" customHeight="1">
       <c r="B505" t="n">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506">
+    <row r="506" ht="14.45" customHeight="1">
       <c r="B506" t="n">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507">
+    <row r="507" ht="14.45" customHeight="1">
       <c r="B507" t="n">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" ht="14.45" customHeight="1">
       <c r="B508" t="n">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509">
+    <row r="509" ht="14.45" customHeight="1">
       <c r="B509" t="n">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510">
+    <row r="510" ht="14.45" customHeight="1">
       <c r="B510" t="n">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511">
+    <row r="511" ht="14.45" customHeight="1">
       <c r="B511" t="n">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512">
+    <row r="512" ht="14.45" customHeight="1">
       <c r="B512" t="n">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513">
+    <row r="513" ht="14.45" customHeight="1">
       <c r="B513" t="n">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514">
+    <row r="514" ht="14.45" customHeight="1">
       <c r="B514" t="n">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515">
+    <row r="515" ht="14.45" customHeight="1">
       <c r="B515" t="n">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516">
+    <row r="516" ht="14.45" customHeight="1">
       <c r="B516" t="n">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517">
+    <row r="517" ht="14.45" customHeight="1">
       <c r="B517" t="n">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518">
+    <row r="518" ht="14.45" customHeight="1">
       <c r="B518" t="n">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519">
+    <row r="519" ht="14.45" customHeight="1">
       <c r="B519" t="n">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520">
+    <row r="520" ht="14.45" customHeight="1">
       <c r="B520" t="n">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521">
+    <row r="521" ht="14.45" customHeight="1">
       <c r="B521" t="n">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522">
+    <row r="522" ht="15" customHeight="1">
       <c r="B522" t="n">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
     <row r="523" ht="15" customHeight="1">
       <c r="B523" t="n">
-        <v>3513</v>
+        <v>3514</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
     <row r="524" ht="15" customHeight="1">
       <c r="B524" t="n">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -8712,9 +8726,6 @@
       <c r="Q524" s="4" t="n"/>
     </row>
     <row r="525" ht="15" customHeight="1">
-      <c r="B525" t="n">
-        <v>3515</v>
-      </c>
       <c r="F525" t="inlineStr">
         <is>
           <t>A</t>
@@ -8759,17 +8770,8 @@
       <c r="O529" s="4" t="n"/>
       <c r="Q529" s="4" t="n"/>
     </row>
-    <row r="530" ht="15" customHeight="1">
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O530" s="4" t="n"/>
-      <c r="Q530" s="4" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B540"/>
+  <autoFilter ref="B539"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId2"/>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -5458,8 +5458,33 @@
       <c r="Q80" s="4" t="n"/>
     </row>
     <row r="81" ht="14.45" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="B81" t="n">
         <v>3072</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GXO Direct Multi Tenant:Patrick Ta</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>req</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>4455 Regent Blvd  Irving, TX 75063</t>
+        </is>
       </c>
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -442,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -562,9 +562,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -584,13 +581,9 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -633,7 +626,6 @@
     <xf numFmtId="14" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1154,7 +1146,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="15.7109375" customWidth="1" min="1" max="1"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="126" min="2" max="2"/>
     <col width="36.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="72.42578125" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
@@ -1184,14 +1176,14 @@
     <col width="16.140625" customWidth="1" style="53" min="31" max="31"/>
     <col width="22.85546875" customWidth="1" min="32" max="32"/>
     <col width="17.28515625" customWidth="1" min="33" max="33"/>
-    <col width="16.28515625" customWidth="1" style="144" min="34" max="34"/>
+    <col width="16.28515625" customWidth="1" style="140" min="34" max="34"/>
     <col width="22.85546875" customWidth="1" min="35" max="36"/>
     <col width="31.85546875" customWidth="1" min="37" max="37"/>
     <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
     <col width="33.28515625" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.9" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1283,7 +1275,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.45" customFormat="1" customHeight="1" s="62">
+    <row r="2" customFormat="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1348,17 +1340,17 @@
           <t>1551 Normantown Rd, Romeoville, IL</t>
         </is>
       </c>
-      <c r="O2" s="91" t="inlineStr">
+      <c r="O2" s="88" t="inlineStr">
         <is>
           <t>6:30am - 12:30am M-F CST</t>
         </is>
       </c>
-      <c r="P2" s="124" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>hasbromanagement@gxo.com</t>
         </is>
       </c>
-      <c r="Q2" s="88" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>cecelia.fox@gxo.com</t>
         </is>
@@ -1367,12 +1359,12 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" ht="14.45" customHeight="1">
-      <c r="A3" s="122" t="n"/>
+    <row r="3">
+      <c r="A3" s="118" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
       </c>
-      <c r="C3" s="95" t="inlineStr">
+      <c r="C3" s="92" t="inlineStr">
         <is>
           <t>Hasbro</t>
         </is>
@@ -1433,8 +1425,8 @@
         </is>
       </c>
       <c r="O3" s="26" t="n"/>
-      <c r="P3" s="124" t="n"/>
-      <c r="Q3" s="88" t="n"/>
+      <c r="P3" s="120" t="n"/>
+      <c r="Q3" s="85" t="n"/>
       <c r="R3" s="23" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1" thickBot="1">
@@ -1506,13 +1498,13 @@
           <t>2353 U.S. 130, Dayton, NJ</t>
         </is>
       </c>
-      <c r="O4" s="136" t="inlineStr">
+      <c r="O4" s="132" t="inlineStr">
         <is>
           <t xml:space="preserve"> 7:00am – 3:30pm M-F EST</t>
         </is>
       </c>
-      <c r="P4" s="124" t="n"/>
-      <c r="Q4" s="88" t="inlineStr">
+      <c r="P4" s="120" t="n"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>todd.pearce@gxo.com</t>
         </is>
@@ -1521,7 +1513,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" ht="28.9" customHeight="1">
+    <row r="5">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1571,25 +1563,25 @@
         </is>
       </c>
       <c r="P5" s="63" t="n"/>
-      <c r="Q5" s="65" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>steve.charnes@gxo.com, tim.serfess@gxo.com</t>
         </is>
       </c>
-      <c r="R5" s="66" t="n">
+      <c r="R5" s="65" t="n">
         <v>45117</v>
       </c>
     </row>
-    <row r="6" ht="14.45" customHeight="1">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
         </is>
       </c>
-      <c r="B6" s="104" t="n">
+      <c r="B6" s="101" t="n">
         <v>3006</v>
       </c>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>Darigold</t>
         </is>
@@ -1625,22 +1617,22 @@
           <t>4719 Market St, Boise, ID</t>
         </is>
       </c>
-      <c r="O6" s="108" t="inlineStr">
+      <c r="O6" s="105" t="inlineStr">
         <is>
           <t>5:00 AM-12:30 AM MTN</t>
         </is>
       </c>
       <c r="P6" s="27" t="n"/>
-      <c r="Q6" s="65" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>john.ozmon@gxo.com</t>
         </is>
       </c>
-      <c r="R6" s="66" t="n">
+      <c r="R6" s="65" t="n">
         <v>45140</v>
       </c>
     </row>
-    <row r="7" ht="14.45" customHeight="1">
+    <row r="7">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1709,7 +1701,7 @@
           <t>24/7 MTN</t>
         </is>
       </c>
-      <c r="Q7" s="88" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>john.ozmon@gxo.com</t>
         </is>
@@ -1718,7 +1710,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8" ht="14.45" customHeight="1">
+    <row r="8">
       <c r="B8" s="27" t="n">
         <v>3007</v>
       </c>
@@ -1738,12 +1730,12 @@
       <c r="L8" s="27" t="n"/>
       <c r="M8" s="27" t="n"/>
       <c r="N8" s="27" t="n"/>
-      <c r="O8" s="108" t="n"/>
+      <c r="O8" s="105" t="n"/>
       <c r="P8" s="27" t="n"/>
-      <c r="Q8" s="108" t="n"/>
-      <c r="R8" s="66" t="n"/>
-    </row>
-    <row r="9" ht="14.45" customHeight="1">
+      <c r="Q8" s="105" t="n"/>
+      <c r="R8" s="65" t="n"/>
+    </row>
+    <row r="9">
       <c r="B9" t="n">
         <v>3008</v>
       </c>
@@ -1817,7 +1809,7 @@
           <t>Routing.alps@gxo.com</t>
         </is>
       </c>
-      <c r="Q9" s="88" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>john.hunter001@gxo.com</t>
         </is>
@@ -1895,12 +1887,12 @@
           <t>7:00 am to 3:30 pm</t>
         </is>
       </c>
-      <c r="P10" s="124" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>SodaStreamManteca@gxo.com</t>
         </is>
       </c>
-      <c r="Q10" s="88" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>rafa.duenas@gxo.com   , Ron.biggs@gxo.com</t>
         </is>
@@ -1915,10 +1907,10 @@
           <t>Shawn</t>
         </is>
       </c>
-      <c r="B11" s="79" t="n">
+      <c r="B11" s="78" t="n">
         <v>3009</v>
       </c>
-      <c r="C11" s="79" t="inlineStr">
+      <c r="C11" s="78" t="inlineStr">
         <is>
           <t>Soda Stream</t>
         </is>
@@ -1928,7 +1920,7 @@
           <t>NP12</t>
         </is>
       </c>
-      <c r="E11" s="79" t="inlineStr">
+      <c r="E11" s="78" t="inlineStr">
         <is>
           <t>PR13</t>
         </is>
@@ -1938,7 +1930,7 @@
           <t>PR13A</t>
         </is>
       </c>
-      <c r="G11" s="79" t="inlineStr">
+      <c r="G11" s="78" t="inlineStr">
         <is>
           <t>CPO</t>
         </is>
@@ -1953,7 +1945,7 @@
           <t>2021.1.1.66</t>
         </is>
       </c>
-      <c r="J11" s="79" t="inlineStr">
+      <c r="J11" s="78" t="inlineStr">
         <is>
           <t>2021.1.1.28.3</t>
         </is>
@@ -1963,7 +1955,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L11" s="79" t="inlineStr">
+      <c r="L11" s="78" t="inlineStr">
         <is>
           <t>exec-wms-gxo-sodastream-east-les</t>
         </is>
@@ -1973,27 +1965,27 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N11" s="79" t="inlineStr">
+      <c r="N11" s="78" t="inlineStr">
         <is>
           <t>4406 Industrial Park Rd, Camp Hill, PA</t>
         </is>
       </c>
-      <c r="O11" s="80" t="inlineStr">
+      <c r="O11" s="79" t="inlineStr">
         <is>
           <t>5:30 am EST - 7 pm EST</t>
         </is>
       </c>
-      <c r="P11" s="79" t="n"/>
-      <c r="Q11" s="81" t="inlineStr">
+      <c r="P11" s="78" t="n"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>chris.menges@gxo.com</t>
         </is>
       </c>
-      <c r="R11" s="145" t="n">
+      <c r="R11" s="141" t="n">
         <v>45516</v>
       </c>
     </row>
-    <row r="12" ht="43.15" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2037,22 +2029,22 @@
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="J12" s="91" t="inlineStr">
+      <c r="J12" s="88" t="inlineStr">
         <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="K12" s="91" t="inlineStr">
+      <c r="K12" s="88" t="inlineStr">
         <is>
           <t>be40-01p-eus2</t>
         </is>
       </c>
-      <c r="L12" s="91" t="inlineStr">
+      <c r="L12" s="88" t="inlineStr">
         <is>
           <t>exec-wms-gxo-starbucks-les</t>
         </is>
       </c>
-      <c r="M12" s="91" t="inlineStr">
+      <c r="M12" s="88" t="inlineStr">
         <is>
           <t>gxoe-prod</t>
         </is>
@@ -2065,7 +2057,7 @@
         </is>
       </c>
       <c r="O12" s="4" t="n"/>
-      <c r="Q12" s="88" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>rick.kusimoto@gxo.com</t>
         </is>
@@ -2074,7 +2066,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="13" ht="14.45" customFormat="1" customHeight="1" s="27">
+    <row r="13" customFormat="1" s="27">
       <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2128,17 +2120,17 @@
           <t>14901 N Beach St, Fort Worth, TX</t>
         </is>
       </c>
-      <c r="O13" s="108" t="n"/>
-      <c r="Q13" s="108" t="inlineStr">
+      <c r="O13" s="105" t="n"/>
+      <c r="Q13" s="105" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="R13" s="109" t="n">
+      <c r="R13" s="106" t="n">
         <v>45754</v>
       </c>
     </row>
-    <row r="14" ht="14.45" customHeight="1">
+    <row r="14">
       <c r="B14" s="27" t="n">
         <v>3012</v>
       </c>
@@ -2154,12 +2146,12 @@
       <c r="L14" s="27" t="n"/>
       <c r="M14" s="27" t="n"/>
       <c r="N14" s="27" t="n"/>
-      <c r="O14" s="108" t="n"/>
+      <c r="O14" s="105" t="n"/>
       <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="108" t="n"/>
-      <c r="R14" s="66" t="n"/>
-    </row>
-    <row r="15" ht="14.45" customHeight="1">
+      <c r="Q14" s="105" t="n"/>
+      <c r="R14" s="65" t="n"/>
+    </row>
+    <row r="15">
       <c r="B15" s="27" t="n">
         <v>3013</v>
       </c>
@@ -2175,12 +2167,12 @@
       <c r="L15" s="27" t="n"/>
       <c r="M15" s="27" t="n"/>
       <c r="N15" s="27" t="n"/>
-      <c r="O15" s="108" t="n"/>
+      <c r="O15" s="105" t="n"/>
       <c r="P15" s="27" t="n"/>
-      <c r="Q15" s="108" t="n"/>
-      <c r="R15" s="66" t="n"/>
-    </row>
-    <row r="16" ht="14.45" customHeight="1">
+      <c r="Q15" s="105" t="n"/>
+      <c r="R15" s="65" t="n"/>
+    </row>
+    <row r="16">
       <c r="B16" t="n">
         <v>3014</v>
       </c>
@@ -2244,7 +2236,7 @@
           <t>M-F 0800-0130, Sat &amp; Sun 0600-2330 EST</t>
         </is>
       </c>
-      <c r="Q16" s="88" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>john.hecker@gxo.com</t>
         </is>
@@ -2302,23 +2294,23 @@
           <t>3520 Cactus Ave, Bloomington, CA</t>
         </is>
       </c>
-      <c r="O17" s="108" t="inlineStr">
+      <c r="O17" s="105" t="inlineStr">
         <is>
           <t>6:00am - 6:00pm during Peak; 8:am-4:30pm Normal non-peak.  CST</t>
         </is>
       </c>
       <c r="P17" s="27" t="n"/>
-      <c r="Q17" s="65" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>jeremy.hoppe@gxo.com, levale.williams@gxo.com,savy.phauk@gxo.com</t>
         </is>
       </c>
-      <c r="R17" s="66" t="n">
+      <c r="R17" s="65" t="n">
         <v>45201</v>
       </c>
     </row>
-    <row r="18" ht="29.25" customFormat="1" customHeight="1" s="79">
-      <c r="A18" s="79" t="inlineStr">
+    <row r="18" ht="29.25" customFormat="1" customHeight="1" s="78">
+      <c r="A18" s="78" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
         </is>
@@ -2386,18 +2378,18 @@
           <t>7140 N. CAJON BLVD.  San Bernandino, CA</t>
         </is>
       </c>
-      <c r="O18" s="91" t="inlineStr">
+      <c r="O18" s="88" t="inlineStr">
         <is>
           <t xml:space="preserve">
 7:00 am to 3:30 pm PST</t>
         </is>
       </c>
-      <c r="P18" s="124" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>CorsairSoCal@gxo.com</t>
         </is>
       </c>
-      <c r="Q18" s="88" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>rafa.duenas@gxo.com</t>
         </is>
@@ -2470,21 +2462,21 @@
           <t>be40-02f-eus2</t>
         </is>
       </c>
-      <c r="N19" s="105" t="inlineStr">
+      <c r="N19" s="102" t="inlineStr">
         <is>
           <t>1695 Drew Rd. Unit 2, Mississauga, Ontario, CA, L5S 1J5</t>
         </is>
       </c>
-      <c r="O19" s="91" t="inlineStr">
+      <c r="O19" s="88" t="inlineStr">
         <is>
           <t>7:30 am to 4:30 pm EST</t>
         </is>
       </c>
-      <c r="P19" s="124" t="n"/>
-      <c r="Q19" s="88" t="n"/>
+      <c r="P19" s="120" t="n"/>
+      <c r="Q19" s="85" t="n"/>
       <c r="R19" s="23" t="n"/>
     </row>
-    <row r="20" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="20" ht="45" customFormat="1" customHeight="1" s="27">
       <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2520,7 +2512,7 @@
         </is>
       </c>
       <c r="O20" s="4" t="n"/>
-      <c r="Q20" s="88" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
@@ -2529,7 +2521,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="21" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="21" ht="45" customFormat="1" customHeight="1" s="27">
       <c r="B21" t="n">
         <v>3018</v>
       </c>
@@ -2565,13 +2557,13 @@
         </is>
       </c>
       <c r="O21" s="4" t="n"/>
-      <c r="Q21" s="88" t="inlineStr">
+      <c r="Q21" s="85" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="22" ht="45" customFormat="1" customHeight="1" s="27">
       <c r="B22" t="n">
         <v>3019</v>
       </c>
@@ -2607,13 +2599,13 @@
         </is>
       </c>
       <c r="O22" s="4" t="n"/>
-      <c r="Q22" s="88" t="inlineStr">
+      <c r="Q22" s="85" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="43.15" customHeight="1">
+    <row r="23" ht="45" customHeight="1">
       <c r="B23" t="n">
         <v>3020</v>
       </c>
@@ -2649,7 +2641,7 @@
         </is>
       </c>
       <c r="O23" s="4" t="n"/>
-      <c r="Q23" s="88" t="inlineStr">
+      <c r="Q23" s="85" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
@@ -2696,7 +2688,7 @@
         </is>
       </c>
       <c r="O24" s="4" t="n"/>
-      <c r="Q24" s="88" t="inlineStr">
+      <c r="Q24" s="85" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
@@ -2777,7 +2769,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="26" ht="28.9" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2841,7 +2833,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N26" s="131" t="inlineStr">
+      <c r="N26" s="127" t="inlineStr">
         <is>
           <t>6195 Highway 51 N, Suite 200, Horn Lake MS</t>
         </is>
@@ -2852,16 +2844,16 @@
         </is>
       </c>
       <c r="P26" s="27" t="n"/>
-      <c r="Q26" s="65" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>steve.charnes@gxo.com, tim.serfess@gxo.com</t>
         </is>
       </c>
-      <c r="R26" s="66" t="n">
+      <c r="R26" s="65" t="n">
         <v>45432</v>
       </c>
     </row>
-    <row r="27" ht="28.9" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2909,25 +2901,25 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N27" s="108" t="inlineStr">
+      <c r="N27" s="105" t="inlineStr">
         <is>
           <t>1500 Bellwood Road, Richmond, VA, 23237</t>
         </is>
       </c>
-      <c r="O27" s="108" t="n"/>
+      <c r="O27" s="105" t="n"/>
       <c r="P27" s="27" t="n"/>
-      <c r="Q27" s="65" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>dexter.sallet@gxo.com</t>
         </is>
       </c>
-      <c r="R27" s="66" t="inlineStr">
+      <c r="R27" s="65" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="43.9" customHeight="1" thickBot="1">
+    <row r="28" ht="45.75" customHeight="1" thickBot="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2988,14 +2980,14 @@
 USA</t>
         </is>
       </c>
-      <c r="O28" s="92" t="inlineStr">
+      <c r="O28" s="89" t="inlineStr">
         <is>
           <t>NEW TBD</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
     </row>
-    <row r="29" ht="14.45" customHeight="1">
+    <row r="29">
       <c r="B29" t="n">
         <v>3026</v>
       </c>
@@ -3066,7 +3058,7 @@
       </c>
       <c r="Q29" s="4" t="n"/>
     </row>
-    <row r="30" ht="14.45" customHeight="1">
+    <row r="30">
       <c r="B30" t="n">
         <v>3026</v>
       </c>
@@ -3103,7 +3095,7 @@
       <c r="O30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
     </row>
-    <row r="31" ht="14.45" customHeight="1">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3168,13 +3160,8 @@
         </is>
       </c>
       <c r="O31" s="4" t="n"/>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>mailto:brandon.conner@gxo.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28.9" customHeight="1">
+    </row>
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3239,19 +3226,14 @@
           <t>be40-028-eus2</t>
         </is>
       </c>
-      <c r="N32" s="101" t="inlineStr">
+      <c r="N32" s="98" t="inlineStr">
         <is>
           <t>6111 Grayson Rd Harrisburg, PA</t>
         </is>
       </c>
       <c r="O32" s="4" t="n"/>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>mailto:brandon.conner@gxo.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="43.15" customHeight="1">
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3293,13 +3275,8 @@
         </is>
       </c>
       <c r="O33" s="4" t="n"/>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>mailto:brandon.conner@gxo.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28.9" customHeight="1">
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3355,13 +3332,8 @@
         </is>
       </c>
       <c r="O34" s="4" t="n"/>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>mailto:brandon.conner@gxo.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="43.15" customHeight="1">
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3499,7 +3471,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" ht="43.15" customHeight="1">
+    <row r="37" ht="45" customHeight="1">
       <c r="B37" t="n">
         <v>3035</v>
       </c>
@@ -3568,7 +3540,7 @@
       <c r="O37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
     </row>
-    <row r="38" ht="57.6" customHeight="1">
+    <row r="38" ht="60" customHeight="1">
       <c r="B38" t="n">
         <v>3035</v>
       </c>
@@ -3633,76 +3605,76 @@
       <c r="O38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
     </row>
-    <row r="39" ht="14.45" customFormat="1" customHeight="1" s="138">
-      <c r="A39" s="138" t="inlineStr">
+    <row r="39" customFormat="1" s="134">
+      <c r="A39" s="134" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="B39" s="143" t="inlineStr">
+      <c r="B39" s="139" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C39" s="138" t="inlineStr">
+      <c r="C39" s="134" t="inlineStr">
         <is>
           <t>QL Template (AMAPAC)</t>
         </is>
       </c>
-      <c r="D39" s="138" t="inlineStr">
+      <c r="D39" s="134" t="inlineStr">
         <is>
           <t>NP25</t>
         </is>
       </c>
-      <c r="E39" s="138" t="inlineStr">
+      <c r="E39" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F39" s="138" t="inlineStr">
+      <c r="F39" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G39" s="138" t="inlineStr">
+      <c r="G39" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H39" s="138" t="inlineStr">
+      <c r="H39" s="134" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I39" s="138" t="inlineStr">
+      <c r="I39" s="134" t="inlineStr">
         <is>
           <t>2023.1.0.50.0</t>
         </is>
       </c>
-      <c r="J39" s="138" t="inlineStr">
+      <c r="J39" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K39" s="138" t="inlineStr">
+      <c r="K39" s="134" t="inlineStr">
         <is>
           <t>be40-02j-eus2</t>
         </is>
       </c>
-      <c r="L39" s="138" t="inlineStr">
+      <c r="L39" s="134" t="inlineStr">
         <is>
           <t>exec-wms-gxo-les</t>
         </is>
       </c>
-      <c r="M39" s="138" t="inlineStr">
+      <c r="M39" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O39" s="140" t="n"/>
-      <c r="Q39" s="140" t="n"/>
-    </row>
-    <row r="40" ht="14.45" customHeight="1">
+      <c r="O39" s="136" t="n"/>
+      <c r="Q39" s="136" t="n"/>
+    </row>
+    <row r="40">
       <c r="B40" t="n">
         <v>3031</v>
       </c>
@@ -3769,7 +3741,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" ht="57.6" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3837,7 +3809,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="28.9" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3909,7 +3881,7 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" ht="43.15" customHeight="1">
+    <row r="43" ht="45" customHeight="1">
       <c r="B43" t="n">
         <v>3035</v>
       </c>
@@ -3953,7 +3925,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" ht="28.9" customHeight="1">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4026,7 +3998,7 @@
       </c>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45" ht="14.45" customHeight="1">
+    <row r="45">
       <c r="A45" t="inlineStr">
         <is>
           <t>US</t>
@@ -4059,7 +4031,7 @@
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" ht="41.45" customHeight="1">
+    <row r="46" ht="40.5" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4073,17 +4045,17 @@
           <t>Kumho (EU)</t>
         </is>
       </c>
-      <c r="D46" s="107" t="inlineStr">
+      <c r="D46" s="104" t="inlineStr">
         <is>
           <t>NP4</t>
         </is>
       </c>
-      <c r="E46" s="107" t="inlineStr">
+      <c r="E46" s="104" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F46" s="107" t="n"/>
+      <c r="F46" s="104" t="n"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>GE1</t>
@@ -4109,7 +4081,7 @@
           <t>exec-wms-gxo-kumho-les</t>
         </is>
       </c>
-      <c r="N46" s="106" t="inlineStr">
+      <c r="N46" s="103" t="inlineStr">
         <is>
           <t>GXO Marchamalo 2 
 Calle el Ventorro
@@ -4119,7 +4091,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" ht="28.9" customHeight="1">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4182,7 +4154,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48" ht="14.45" customHeight="1">
+    <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4239,7 +4211,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" ht="43.15" customHeight="1">
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>US</t>
@@ -4283,76 +4255,76 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" ht="14.45" customFormat="1" customHeight="1" s="138">
-      <c r="A50" s="138" t="inlineStr">
+    <row r="50" customFormat="1" s="134">
+      <c r="A50" s="134" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="B50" s="143" t="inlineStr">
+      <c r="B50" s="139" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C50" s="138" t="inlineStr">
+      <c r="C50" s="134" t="inlineStr">
         <is>
           <t>QL Template (EU)</t>
         </is>
       </c>
-      <c r="D50" s="138" t="inlineStr">
+      <c r="D50" s="134" t="inlineStr">
         <is>
           <t>NP5</t>
         </is>
       </c>
-      <c r="E50" s="138" t="inlineStr">
+      <c r="E50" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F50" s="138" t="inlineStr">
+      <c r="F50" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G50" s="138" t="inlineStr">
+      <c r="G50" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H50" s="138" t="inlineStr">
+      <c r="H50" s="134" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I50" s="138" t="inlineStr">
+      <c r="I50" s="134" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="J50" s="138" t="inlineStr">
+      <c r="J50" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K50" s="138" t="inlineStr">
+      <c r="K50" s="134" t="inlineStr">
         <is>
           <t>Not Setup</t>
         </is>
       </c>
-      <c r="L50" s="138" t="inlineStr">
+      <c r="L50" s="134" t="inlineStr">
         <is>
           <t>exec-wms-gxo-les</t>
         </is>
       </c>
-      <c r="M50" s="138" t="inlineStr">
+      <c r="M50" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O50" s="140" t="n"/>
-      <c r="Q50" s="140" t="n"/>
-    </row>
-    <row r="51" ht="14.45" customHeight="1">
+      <c r="O50" s="136" t="n"/>
+      <c r="Q50" s="136" t="n"/>
+    </row>
+    <row r="51">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4379,7 +4351,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52" ht="14.45" customHeight="1">
+    <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4436,7 +4408,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53" ht="14.45" customHeight="1">
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4463,7 +4435,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54" ht="14.45" customHeight="1">
+    <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4495,7 +4467,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55" ht="14.45" customHeight="1">
+    <row r="55">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4527,7 +4499,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56" ht="14.45" customHeight="1">
+    <row r="56">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4559,7 +4531,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57" ht="14.45" customHeight="1">
+    <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4591,7 +4563,7 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58" ht="14.45" customHeight="1">
+    <row r="58">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4623,7 +4595,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59" ht="14.45" customHeight="1">
+    <row r="59">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4655,7 +4627,7 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60" ht="14.45" customHeight="1">
+    <row r="60">
       <c r="A60" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4687,7 +4659,7 @@
       <c r="O60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
     </row>
-    <row r="61" ht="14.45" customHeight="1">
+    <row r="61">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4719,7 +4691,7 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62" ht="14.45" customHeight="1">
+    <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4751,7 +4723,7 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63" ht="14.45" customHeight="1">
+    <row r="63">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4783,7 +4755,7 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64" ht="14.45" customHeight="1">
+    <row r="64">
       <c r="B64" t="n">
         <v>3056</v>
       </c>
@@ -4810,7 +4782,7 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" ht="43.15" customHeight="1">
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>US</t>
@@ -4854,95 +4826,95 @@
       <c r="O65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
     </row>
-    <row r="66" ht="14.45" customFormat="1" customHeight="1" s="138">
-      <c r="A66" s="138" t="inlineStr">
+    <row r="66" customFormat="1" s="134">
+      <c r="A66" s="134" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="B66" s="139" t="inlineStr">
+      <c r="B66" s="135" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C66" s="138" t="inlineStr">
+      <c r="C66" s="134" t="inlineStr">
         <is>
           <t>QL Dev/Test Env for NP5</t>
         </is>
       </c>
-      <c r="D66" s="138" t="inlineStr">
+      <c r="D66" s="134" t="inlineStr">
         <is>
           <t>NP14</t>
         </is>
       </c>
-      <c r="E66" s="138" t="inlineStr">
+      <c r="E66" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F66" s="138" t="inlineStr">
+      <c r="F66" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G66" s="138" t="inlineStr">
+      <c r="G66" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H66" s="138" t="inlineStr">
+      <c r="H66" s="134" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="O66" s="140" t="n"/>
-      <c r="Q66" s="140" t="n"/>
-    </row>
-    <row r="67" ht="14.45" customFormat="1" customHeight="1" s="138">
-      <c r="A67" s="138" t="inlineStr">
+      <c r="O66" s="136" t="n"/>
+      <c r="Q66" s="136" t="n"/>
+    </row>
+    <row r="67" customFormat="1" s="134">
+      <c r="A67" s="134" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="B67" s="139" t="inlineStr">
+      <c r="B67" s="135" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C67" s="138" t="inlineStr">
+      <c r="C67" s="134" t="inlineStr">
         <is>
           <t>QL DEV/Test Env for NP25</t>
         </is>
       </c>
-      <c r="D67" s="138" t="inlineStr">
+      <c r="D67" s="134" t="inlineStr">
         <is>
           <t>NP39</t>
         </is>
       </c>
-      <c r="E67" s="138" t="inlineStr">
+      <c r="E67" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F67" s="138" t="inlineStr">
+      <c r="F67" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G67" s="138" t="inlineStr">
+      <c r="G67" s="134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H67" s="138" t="inlineStr">
+      <c r="H67" s="134" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="O67" s="140" t="n"/>
-      <c r="Q67" s="140" t="n"/>
-    </row>
-    <row r="68" ht="43.15" customHeight="1">
+      <c r="O67" s="136" t="n"/>
+      <c r="Q67" s="136" t="n"/>
+    </row>
+    <row r="68" ht="45" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4981,7 +4953,7 @@
       <c r="O68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
     </row>
-    <row r="69" ht="14.45" customHeight="1">
+    <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5013,7 +4985,7 @@
       <c r="O69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
     </row>
-    <row r="70" ht="14.45" customHeight="1">
+    <row r="70">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5045,7 +5017,7 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71" ht="14.45" customHeight="1">
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5087,7 +5059,7 @@
       <c r="O71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
     </row>
-    <row r="72" ht="43.15" customHeight="1">
+    <row r="72" ht="45" customHeight="1">
       <c r="B72" t="n">
         <v>3063</v>
       </c>
@@ -5121,7 +5093,7 @@
       <c r="O72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
     </row>
-    <row r="73" ht="14.45" customHeight="1">
+    <row r="73">
       <c r="A73" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5155,7 +5127,7 @@
       <c r="O73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
     </row>
-    <row r="74" ht="57.6" customHeight="1">
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5194,7 +5166,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" ht="43.15" customHeight="1">
+    <row r="75" ht="45" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5233,7 +5205,7 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" ht="28.9" customHeight="1">
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5305,7 +5277,7 @@
       <c r="O76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
     </row>
-    <row r="77" ht="43.15" customHeight="1">
+    <row r="77" ht="45" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
@@ -5344,7 +5316,7 @@
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78" ht="14.45" customHeight="1">
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
           <t>US</t>
@@ -5386,7 +5358,7 @@
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79" ht="43.15" customHeight="1">
+    <row r="79" ht="45" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
           <t>US</t>
@@ -5435,7 +5407,7 @@
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80" ht="14.45" customHeight="1">
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
           <t>US</t>
@@ -5457,7 +5429,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81" ht="14.45" customHeight="1">
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
           <t>US</t>
@@ -5489,1995 +5461,1995 @@
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" ht="14.45" customHeight="1">
+    <row r="82">
       <c r="B82" t="n">
         <v>3073</v>
       </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" ht="14.45" customHeight="1">
+    <row r="83">
       <c r="B83" t="n">
         <v>3074</v>
       </c>
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" ht="14.45" customHeight="1">
+    <row r="84">
       <c r="B84" t="n">
         <v>3075</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" ht="14.45" customHeight="1">
+    <row r="85">
       <c r="B85" t="n">
         <v>3076</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" ht="14.45" customHeight="1">
+    <row r="86">
       <c r="B86" t="n">
         <v>3077</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" ht="14.45" customHeight="1">
+    <row r="87">
       <c r="B87" t="n">
         <v>3078</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" ht="14.45" customHeight="1">
+    <row r="88">
       <c r="B88" t="n">
         <v>3079</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" ht="14.45" customHeight="1">
+    <row r="89">
       <c r="B89" t="n">
         <v>3080</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" ht="14.45" customHeight="1">
+    <row r="90">
       <c r="B90" t="n">
         <v>3081</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" ht="14.45" customHeight="1">
+    <row r="91">
       <c r="B91" t="n">
         <v>3082</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" ht="14.45" customHeight="1">
+    <row r="92">
       <c r="B92" t="n">
         <v>3083</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" ht="14.45" customHeight="1">
+    <row r="93">
       <c r="B93" t="n">
         <v>3084</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" ht="14.45" customHeight="1">
+    <row r="94">
       <c r="B94" t="n">
         <v>3085</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" ht="14.45" customHeight="1">
+    <row r="95">
       <c r="B95" t="n">
         <v>3086</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" ht="14.45" customHeight="1">
+    <row r="96">
       <c r="B96" t="n">
         <v>3087</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" ht="14.45" customHeight="1">
+    <row r="97">
       <c r="B97" t="n">
         <v>3088</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" ht="14.45" customHeight="1">
+    <row r="98">
       <c r="B98" t="n">
         <v>3089</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" ht="14.45" customHeight="1">
+    <row r="99">
       <c r="B99" t="n">
         <v>3090</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" ht="14.45" customHeight="1">
+    <row r="100">
       <c r="B100" t="n">
         <v>3091</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" ht="14.45" customHeight="1">
+    <row r="101">
       <c r="B101" t="n">
         <v>3092</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" ht="14.45" customHeight="1">
+    <row r="102">
       <c r="B102" t="n">
         <v>3093</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" ht="14.45" customHeight="1">
+    <row r="103">
       <c r="B103" t="n">
         <v>3094</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" ht="14.45" customHeight="1">
+    <row r="104">
       <c r="B104" t="n">
         <v>3095</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" ht="14.45" customHeight="1">
+    <row r="105">
       <c r="B105" t="n">
         <v>3096</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" ht="14.45" customHeight="1">
+    <row r="106">
       <c r="B106" t="n">
         <v>3097</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" ht="14.45" customHeight="1">
+    <row r="107">
       <c r="B107" t="n">
         <v>3098</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" ht="14.45" customHeight="1">
+    <row r="108">
       <c r="B108" t="n">
         <v>3099</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" ht="14.45" customHeight="1">
+    <row r="109">
       <c r="B109" t="n">
         <v>3100</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" ht="14.45" customHeight="1">
+    <row r="110">
       <c r="B110" t="n">
         <v>3101</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" ht="14.45" customHeight="1">
+    <row r="111">
       <c r="B111" t="n">
         <v>3102</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" ht="14.45" customHeight="1">
+    <row r="112">
       <c r="B112" t="n">
         <v>3103</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" ht="14.45" customHeight="1">
+    <row r="113">
       <c r="B113" t="n">
         <v>3104</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" ht="14.45" customHeight="1">
+    <row r="114">
       <c r="B114" t="n">
         <v>3105</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" ht="14.45" customHeight="1">
+    <row r="115">
       <c r="B115" t="n">
         <v>3106</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" ht="14.45" customHeight="1">
+    <row r="116">
       <c r="B116" t="n">
         <v>3107</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" ht="14.45" customHeight="1">
+    <row r="117">
       <c r="B117" t="n">
         <v>3108</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" ht="14.45" customHeight="1">
+    <row r="118">
       <c r="B118" t="n">
         <v>3109</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" ht="14.45" customHeight="1">
+    <row r="119">
       <c r="B119" t="n">
         <v>3110</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" ht="14.45" customHeight="1">
+    <row r="120">
       <c r="B120" t="n">
         <v>3111</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" ht="14.45" customHeight="1">
+    <row r="121">
       <c r="B121" t="n">
         <v>3112</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" ht="14.45" customHeight="1">
+    <row r="122">
       <c r="B122" t="n">
         <v>3113</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" ht="14.45" customHeight="1">
+    <row r="123">
       <c r="B123" t="n">
         <v>3114</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" ht="14.45" customHeight="1">
+    <row r="124">
       <c r="B124" t="n">
         <v>3115</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" ht="14.45" customHeight="1">
+    <row r="125">
       <c r="B125" t="n">
         <v>3116</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" ht="14.45" customHeight="1">
+    <row r="126">
       <c r="B126" t="n">
         <v>3117</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" ht="14.45" customHeight="1">
+    <row r="127">
       <c r="B127" t="n">
         <v>3118</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" ht="14.45" customHeight="1">
+    <row r="128">
       <c r="B128" t="n">
         <v>3119</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" ht="14.45" customHeight="1">
+    <row r="129">
       <c r="B129" t="n">
         <v>3120</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" ht="14.45" customHeight="1">
+    <row r="130">
       <c r="B130" t="n">
         <v>3121</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" ht="14.45" customHeight="1">
+    <row r="131">
       <c r="B131" t="n">
         <v>3122</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" ht="14.45" customHeight="1">
+    <row r="132">
       <c r="B132" t="n">
         <v>3123</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" ht="14.45" customHeight="1">
+    <row r="133">
       <c r="B133" t="n">
         <v>3124</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" ht="14.45" customHeight="1">
+    <row r="134">
       <c r="B134" t="n">
         <v>3125</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" ht="14.45" customHeight="1">
+    <row r="135">
       <c r="B135" t="n">
         <v>3126</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" ht="14.45" customHeight="1">
+    <row r="136">
       <c r="B136" t="n">
         <v>3127</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" ht="14.45" customHeight="1">
+    <row r="137">
       <c r="B137" t="n">
         <v>3128</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" ht="14.45" customHeight="1">
+    <row r="138">
       <c r="B138" t="n">
         <v>3129</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" ht="14.45" customHeight="1">
+    <row r="139">
       <c r="B139" t="n">
         <v>3130</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" ht="14.45" customHeight="1">
+    <row r="140">
       <c r="B140" t="n">
         <v>3131</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" ht="14.45" customHeight="1">
+    <row r="141">
       <c r="B141" t="n">
         <v>3132</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" ht="14.45" customHeight="1">
+    <row r="142">
       <c r="B142" t="n">
         <v>3133</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" ht="14.45" customHeight="1">
+    <row r="143">
       <c r="B143" t="n">
         <v>3134</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" ht="14.45" customHeight="1">
+    <row r="144">
       <c r="B144" t="n">
         <v>3135</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" ht="14.45" customHeight="1">
+    <row r="145">
       <c r="B145" t="n">
         <v>3136</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" ht="14.45" customHeight="1">
+    <row r="146">
       <c r="B146" t="n">
         <v>3137</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" ht="14.45" customHeight="1">
+    <row r="147">
       <c r="B147" t="n">
         <v>3138</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" ht="14.45" customHeight="1">
+    <row r="148">
       <c r="B148" t="n">
         <v>3139</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" ht="14.45" customHeight="1">
+    <row r="149">
       <c r="B149" t="n">
         <v>3140</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" ht="14.45" customHeight="1">
+    <row r="150">
       <c r="B150" t="n">
         <v>3141</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" ht="14.45" customHeight="1">
+    <row r="151">
       <c r="B151" t="n">
         <v>3142</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" ht="14.45" customHeight="1">
+    <row r="152">
       <c r="B152" t="n">
         <v>3143</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" ht="14.45" customHeight="1">
+    <row r="153">
       <c r="B153" t="n">
         <v>3144</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" ht="14.45" customHeight="1">
+    <row r="154">
       <c r="B154" t="n">
         <v>3145</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" ht="14.45" customHeight="1">
+    <row r="155">
       <c r="B155" t="n">
         <v>3146</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" ht="14.45" customHeight="1">
+    <row r="156">
       <c r="B156" t="n">
         <v>3147</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" ht="14.45" customHeight="1">
+    <row r="157">
       <c r="B157" t="n">
         <v>3148</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" ht="14.45" customHeight="1">
+    <row r="158">
       <c r="B158" t="n">
         <v>3149</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" ht="14.45" customHeight="1">
+    <row r="159">
       <c r="B159" t="n">
         <v>3150</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" ht="14.45" customHeight="1">
+    <row r="160">
       <c r="B160" t="n">
         <v>3151</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" ht="14.45" customHeight="1">
+    <row r="161">
       <c r="B161" t="n">
         <v>3152</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" ht="14.45" customHeight="1">
+    <row r="162">
       <c r="B162" t="n">
         <v>3153</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" ht="14.45" customHeight="1">
+    <row r="163">
       <c r="B163" t="n">
         <v>3154</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" ht="14.45" customHeight="1">
+    <row r="164">
       <c r="B164" t="n">
         <v>3155</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" ht="14.45" customHeight="1">
+    <row r="165">
       <c r="B165" t="n">
         <v>3156</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" ht="14.45" customHeight="1">
+    <row r="166">
       <c r="B166" t="n">
         <v>3157</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" ht="14.45" customHeight="1">
+    <row r="167">
       <c r="B167" t="n">
         <v>3158</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" ht="14.45" customHeight="1">
+    <row r="168">
       <c r="B168" t="n">
         <v>3159</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" ht="14.45" customHeight="1">
+    <row r="169">
       <c r="B169" t="n">
         <v>3160</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" ht="14.45" customHeight="1">
+    <row r="170">
       <c r="B170" t="n">
         <v>3161</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" ht="14.45" customHeight="1">
+    <row r="171">
       <c r="B171" t="n">
         <v>3162</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" ht="14.45" customHeight="1">
+    <row r="172">
       <c r="B172" t="n">
         <v>3163</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" ht="14.45" customHeight="1">
+    <row r="173">
       <c r="B173" t="n">
         <v>3164</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" ht="14.45" customHeight="1">
+    <row r="174">
       <c r="B174" t="n">
         <v>3165</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" ht="14.45" customHeight="1">
+    <row r="175">
       <c r="B175" t="n">
         <v>3166</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" ht="14.45" customHeight="1">
+    <row r="176">
       <c r="B176" t="n">
         <v>3167</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" ht="14.45" customHeight="1">
+    <row r="177">
       <c r="B177" t="n">
         <v>3168</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" ht="14.45" customHeight="1">
+    <row r="178">
       <c r="B178" t="n">
         <v>3169</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" ht="14.45" customHeight="1">
+    <row r="179">
       <c r="B179" t="n">
         <v>3170</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" ht="14.45" customHeight="1">
+    <row r="180">
       <c r="B180" t="n">
         <v>3171</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" ht="14.45" customHeight="1">
+    <row r="181">
       <c r="B181" t="n">
         <v>3172</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" ht="14.45" customHeight="1">
+    <row r="182">
       <c r="B182" t="n">
         <v>3173</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" ht="14.45" customHeight="1">
+    <row r="183">
       <c r="B183" t="n">
         <v>3174</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" ht="14.45" customHeight="1">
+    <row r="184">
       <c r="B184" t="n">
         <v>3175</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" ht="14.45" customHeight="1">
+    <row r="185">
       <c r="B185" t="n">
         <v>3176</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" ht="14.45" customHeight="1">
+    <row r="186">
       <c r="B186" t="n">
         <v>3177</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" ht="14.45" customHeight="1">
+    <row r="187">
       <c r="B187" t="n">
         <v>3178</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" ht="14.45" customHeight="1">
+    <row r="188">
       <c r="B188" t="n">
         <v>3179</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" ht="14.45" customHeight="1">
+    <row r="189">
       <c r="B189" t="n">
         <v>3180</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" ht="14.45" customHeight="1">
+    <row r="190">
       <c r="B190" t="n">
         <v>3181</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" ht="14.45" customHeight="1">
+    <row r="191">
       <c r="B191" t="n">
         <v>3182</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" ht="14.45" customHeight="1">
+    <row r="192">
       <c r="B192" t="n">
         <v>3183</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" ht="14.45" customHeight="1">
+    <row r="193">
       <c r="B193" t="n">
         <v>3184</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" ht="14.45" customHeight="1">
+    <row r="194">
       <c r="B194" t="n">
         <v>3185</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" ht="14.45" customHeight="1">
+    <row r="195">
       <c r="B195" t="n">
         <v>3186</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" ht="14.45" customHeight="1">
+    <row r="196">
       <c r="B196" t="n">
         <v>3187</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" ht="14.45" customHeight="1">
+    <row r="197">
       <c r="B197" t="n">
         <v>3188</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" ht="14.45" customHeight="1">
+    <row r="198">
       <c r="B198" t="n">
         <v>3189</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" ht="14.45" customHeight="1">
+    <row r="199">
       <c r="B199" t="n">
         <v>3190</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" ht="14.45" customHeight="1">
+    <row r="200">
       <c r="B200" t="n">
         <v>3191</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" ht="14.45" customHeight="1">
+    <row r="201">
       <c r="B201" t="n">
         <v>3192</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" ht="14.45" customHeight="1">
+    <row r="202">
       <c r="B202" t="n">
         <v>3193</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" ht="14.45" customHeight="1">
+    <row r="203">
       <c r="B203" t="n">
         <v>3194</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" ht="14.45" customHeight="1">
+    <row r="204">
       <c r="B204" t="n">
         <v>3195</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" ht="14.45" customHeight="1">
+    <row r="205">
       <c r="B205" t="n">
         <v>3196</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" ht="14.45" customHeight="1">
+    <row r="206">
       <c r="B206" t="n">
         <v>3197</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" ht="14.45" customHeight="1">
+    <row r="207">
       <c r="B207" t="n">
         <v>3198</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" ht="14.45" customHeight="1">
+    <row r="208">
       <c r="B208" t="n">
         <v>3199</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" ht="14.45" customHeight="1">
+    <row r="209">
       <c r="B209" t="n">
         <v>3200</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" ht="14.45" customHeight="1">
+    <row r="210">
       <c r="B210" t="n">
         <v>3201</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" ht="14.45" customHeight="1">
+    <row r="211">
       <c r="B211" t="n">
         <v>3202</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" ht="14.45" customHeight="1">
+    <row r="212">
       <c r="B212" t="n">
         <v>3203</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" ht="14.45" customHeight="1">
+    <row r="213">
       <c r="B213" t="n">
         <v>3204</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" ht="14.45" customHeight="1">
+    <row r="214">
       <c r="B214" t="n">
         <v>3205</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" ht="14.45" customHeight="1">
+    <row r="215">
       <c r="B215" t="n">
         <v>3206</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" ht="14.45" customHeight="1">
+    <row r="216">
       <c r="B216" t="n">
         <v>3207</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" ht="14.45" customHeight="1">
+    <row r="217">
       <c r="B217" t="n">
         <v>3208</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" ht="14.45" customHeight="1">
+    <row r="218">
       <c r="B218" t="n">
         <v>3209</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" ht="14.45" customHeight="1">
+    <row r="219">
       <c r="B219" t="n">
         <v>3210</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" ht="14.45" customHeight="1">
+    <row r="220">
       <c r="B220" t="n">
         <v>3211</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" ht="14.45" customHeight="1">
+    <row r="221">
       <c r="B221" t="n">
         <v>3212</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" ht="14.45" customHeight="1">
+    <row r="222">
       <c r="B222" t="n">
         <v>3213</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" ht="14.45" customHeight="1">
+    <row r="223">
       <c r="B223" t="n">
         <v>3214</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" ht="14.45" customHeight="1">
+    <row r="224">
       <c r="B224" t="n">
         <v>3215</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" ht="14.45" customHeight="1">
+    <row r="225">
       <c r="B225" t="n">
         <v>3216</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" ht="14.45" customHeight="1">
+    <row r="226">
       <c r="B226" t="n">
         <v>3217</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" ht="14.45" customHeight="1">
+    <row r="227">
       <c r="B227" t="n">
         <v>3218</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" ht="14.45" customHeight="1">
+    <row r="228">
       <c r="B228" t="n">
         <v>3219</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" ht="14.45" customHeight="1">
+    <row r="229">
       <c r="B229" t="n">
         <v>3220</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" ht="14.45" customHeight="1">
+    <row r="230">
       <c r="B230" t="n">
         <v>3221</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" ht="14.45" customHeight="1">
+    <row r="231">
       <c r="B231" t="n">
         <v>3222</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" ht="14.45" customHeight="1">
+    <row r="232">
       <c r="B232" t="n">
         <v>3223</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" ht="14.45" customHeight="1">
+    <row r="233">
       <c r="B233" t="n">
         <v>3224</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" ht="14.45" customHeight="1">
+    <row r="234">
       <c r="B234" t="n">
         <v>3225</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" ht="14.45" customHeight="1">
+    <row r="235">
       <c r="B235" t="n">
         <v>3226</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" ht="14.45" customHeight="1">
+    <row r="236">
       <c r="B236" t="n">
         <v>3227</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" ht="14.45" customHeight="1">
+    <row r="237">
       <c r="B237" t="n">
         <v>3228</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" ht="14.45" customHeight="1">
+    <row r="238">
       <c r="B238" t="n">
         <v>3229</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" ht="14.45" customHeight="1">
+    <row r="239">
       <c r="B239" t="n">
         <v>3230</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" ht="14.45" customHeight="1">
+    <row r="240">
       <c r="B240" t="n">
         <v>3231</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" ht="14.45" customHeight="1">
+    <row r="241">
       <c r="B241" t="n">
         <v>3232</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" ht="14.45" customHeight="1">
+    <row r="242">
       <c r="B242" t="n">
         <v>3233</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" ht="14.45" customHeight="1">
+    <row r="243">
       <c r="B243" t="n">
         <v>3234</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" ht="14.45" customHeight="1">
+    <row r="244">
       <c r="B244" t="n">
         <v>3235</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" ht="14.45" customHeight="1">
+    <row r="245">
       <c r="B245" t="n">
         <v>3236</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" ht="14.45" customHeight="1">
+    <row r="246">
       <c r="B246" t="n">
         <v>3237</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" ht="14.45" customHeight="1">
+    <row r="247">
       <c r="B247" t="n">
         <v>3238</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" ht="14.45" customHeight="1">
+    <row r="248">
       <c r="B248" t="n">
         <v>3239</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" ht="14.45" customHeight="1">
+    <row r="249">
       <c r="B249" t="n">
         <v>3240</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" ht="14.45" customHeight="1">
+    <row r="250">
       <c r="B250" t="n">
         <v>3241</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" ht="14.45" customHeight="1">
+    <row r="251">
       <c r="B251" t="n">
         <v>3242</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" ht="14.45" customHeight="1">
+    <row r="252">
       <c r="B252" t="n">
         <v>3243</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" ht="14.45" customHeight="1">
+    <row r="253">
       <c r="B253" t="n">
         <v>3244</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" ht="14.45" customHeight="1">
+    <row r="254">
       <c r="B254" t="n">
         <v>3245</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" ht="14.45" customHeight="1">
+    <row r="255">
       <c r="B255" t="n">
         <v>3246</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" ht="14.45" customHeight="1">
+    <row r="256">
       <c r="B256" t="n">
         <v>3247</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" ht="14.45" customHeight="1">
+    <row r="257">
       <c r="B257" t="n">
         <v>3248</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" ht="14.45" customHeight="1">
+    <row r="258">
       <c r="B258" t="n">
         <v>3249</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" ht="14.45" customHeight="1">
+    <row r="259">
       <c r="B259" t="n">
         <v>3250</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" ht="14.45" customHeight="1">
+    <row r="260">
       <c r="B260" t="n">
         <v>3251</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" ht="14.45" customHeight="1">
+    <row r="261">
       <c r="B261" t="n">
         <v>3252</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" ht="14.45" customHeight="1">
+    <row r="262">
       <c r="B262" t="n">
         <v>3253</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" ht="14.45" customHeight="1">
+    <row r="263">
       <c r="B263" t="n">
         <v>3254</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" ht="14.45" customHeight="1">
+    <row r="264">
       <c r="B264" t="n">
         <v>3255</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" ht="14.45" customHeight="1">
+    <row r="265">
       <c r="B265" t="n">
         <v>3256</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" ht="14.45" customHeight="1">
+    <row r="266">
       <c r="B266" t="n">
         <v>3257</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" ht="14.45" customHeight="1">
+    <row r="267">
       <c r="B267" t="n">
         <v>3258</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" ht="14.45" customHeight="1">
+    <row r="268">
       <c r="B268" t="n">
         <v>3259</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" ht="14.45" customHeight="1">
+    <row r="269">
       <c r="B269" t="n">
         <v>3260</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" ht="14.45" customHeight="1">
+    <row r="270">
       <c r="B270" t="n">
         <v>3261</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" ht="14.45" customHeight="1">
+    <row r="271">
       <c r="B271" t="n">
         <v>3262</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" ht="14.45" customHeight="1">
+    <row r="272">
       <c r="B272" t="n">
         <v>3263</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" ht="14.45" customHeight="1">
+    <row r="273">
       <c r="B273" t="n">
         <v>3264</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" ht="14.45" customHeight="1">
+    <row r="274">
       <c r="B274" t="n">
         <v>3265</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" ht="14.45" customHeight="1">
+    <row r="275">
       <c r="B275" t="n">
         <v>3266</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" ht="14.45" customHeight="1">
+    <row r="276">
       <c r="B276" t="n">
         <v>3267</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" ht="14.45" customHeight="1">
+    <row r="277">
       <c r="B277" t="n">
         <v>3268</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" ht="14.45" customHeight="1">
+    <row r="278">
       <c r="B278" t="n">
         <v>3269</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" ht="14.45" customHeight="1">
+    <row r="279">
       <c r="B279" t="n">
         <v>3270</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" ht="14.45" customHeight="1">
+    <row r="280">
       <c r="B280" t="n">
         <v>3271</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" ht="14.45" customHeight="1">
+    <row r="281">
       <c r="B281" t="n">
         <v>3272</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" ht="14.45" customHeight="1">
+    <row r="282">
       <c r="B282" t="n">
         <v>3273</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" ht="14.45" customHeight="1">
+    <row r="283">
       <c r="B283" t="n">
         <v>3274</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" ht="14.45" customHeight="1">
+    <row r="284">
       <c r="B284" t="n">
         <v>3275</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" ht="14.45" customHeight="1">
+    <row r="285">
       <c r="B285" t="n">
         <v>3276</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" ht="14.45" customHeight="1">
+    <row r="286">
       <c r="B286" t="n">
         <v>3277</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" ht="14.45" customHeight="1">
+    <row r="287">
       <c r="B287" t="n">
         <v>3278</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" ht="14.45" customHeight="1">
+    <row r="288">
       <c r="B288" t="n">
         <v>3279</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" ht="14.45" customHeight="1">
+    <row r="289">
       <c r="B289" t="n">
         <v>3280</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" ht="14.45" customHeight="1">
+    <row r="290">
       <c r="B290" t="n">
         <v>3281</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" ht="14.45" customHeight="1">
+    <row r="291">
       <c r="B291" t="n">
         <v>3282</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" ht="14.45" customHeight="1">
+    <row r="292">
       <c r="B292" t="n">
         <v>3283</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" ht="14.45" customHeight="1">
+    <row r="293">
       <c r="B293" t="n">
         <v>3284</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" ht="14.45" customHeight="1">
+    <row r="294">
       <c r="B294" t="n">
         <v>3285</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" ht="14.45" customHeight="1">
+    <row r="295">
       <c r="B295" t="n">
         <v>3286</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" ht="14.45" customHeight="1">
+    <row r="296">
       <c r="B296" t="n">
         <v>3287</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" ht="14.45" customHeight="1">
+    <row r="297">
       <c r="B297" t="n">
         <v>3288</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" ht="14.45" customHeight="1">
+    <row r="298">
       <c r="B298" t="n">
         <v>3289</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" ht="14.45" customHeight="1">
+    <row r="299">
       <c r="B299" t="n">
         <v>3290</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" ht="14.45" customHeight="1">
+    <row r="300">
       <c r="B300" t="n">
         <v>3291</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" ht="14.45" customHeight="1">
+    <row r="301">
       <c r="B301" t="n">
         <v>3292</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" ht="14.45" customHeight="1">
+    <row r="302">
       <c r="B302" t="n">
         <v>3293</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" ht="14.45" customHeight="1">
+    <row r="303">
       <c r="B303" t="n">
         <v>3294</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" ht="14.45" customHeight="1">
+    <row r="304">
       <c r="B304" t="n">
         <v>3295</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" ht="14.45" customHeight="1">
+    <row r="305">
       <c r="B305" t="n">
         <v>3296</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" ht="14.45" customHeight="1">
+    <row r="306">
       <c r="B306" t="n">
         <v>3297</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" ht="14.45" customHeight="1">
+    <row r="307">
       <c r="B307" t="n">
         <v>3298</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" ht="14.45" customHeight="1">
+    <row r="308">
       <c r="B308" t="n">
         <v>3299</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" ht="14.45" customHeight="1">
+    <row r="309">
       <c r="B309" t="n">
         <v>3300</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" ht="14.45" customHeight="1">
+    <row r="310">
       <c r="B310" t="n">
         <v>3301</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" ht="14.45" customHeight="1">
+    <row r="311">
       <c r="B311" t="n">
         <v>3302</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" ht="14.45" customHeight="1">
+    <row r="312">
       <c r="B312" t="n">
         <v>3303</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" ht="14.45" customHeight="1">
+    <row r="313">
       <c r="B313" t="n">
         <v>3304</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" ht="14.45" customHeight="1">
+    <row r="314">
       <c r="B314" t="n">
         <v>3305</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" ht="14.45" customHeight="1">
+    <row r="315">
       <c r="B315" t="n">
         <v>3306</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" ht="14.45" customHeight="1">
+    <row r="316">
       <c r="B316" t="n">
         <v>3307</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" ht="14.45" customHeight="1">
+    <row r="317">
       <c r="B317" t="n">
         <v>3308</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" ht="14.45" customHeight="1">
+    <row r="318">
       <c r="B318" t="n">
         <v>3309</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" ht="14.45" customHeight="1">
+    <row r="319">
       <c r="B319" t="n">
         <v>3310</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" ht="14.45" customHeight="1">
+    <row r="320">
       <c r="B320" t="n">
         <v>3311</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" ht="14.45" customHeight="1">
+    <row r="321">
       <c r="B321" t="n">
         <v>3312</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" ht="14.45" customHeight="1">
+    <row r="322">
       <c r="B322" t="n">
         <v>3313</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" ht="14.45" customHeight="1">
+    <row r="323">
       <c r="B323" t="n">
         <v>3314</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" ht="14.45" customHeight="1">
+    <row r="324">
       <c r="B324" t="n">
         <v>3315</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" ht="14.45" customHeight="1">
+    <row r="325">
       <c r="B325" t="n">
         <v>3316</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" ht="14.45" customHeight="1">
+    <row r="326">
       <c r="B326" t="n">
         <v>3317</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" ht="14.45" customHeight="1">
+    <row r="327">
       <c r="B327" t="n">
         <v>3318</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" ht="14.45" customHeight="1">
+    <row r="328">
       <c r="B328" t="n">
         <v>3319</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" ht="14.45" customHeight="1">
+    <row r="329">
       <c r="B329" t="n">
         <v>3320</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" ht="14.45" customHeight="1">
+    <row r="330">
       <c r="B330" t="n">
         <v>3321</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" ht="14.45" customHeight="1">
+    <row r="331">
       <c r="B331" t="n">
         <v>3322</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" ht="14.45" customHeight="1">
+    <row r="332">
       <c r="B332" t="n">
         <v>3323</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" ht="14.45" customHeight="1">
+    <row r="333">
       <c r="B333" t="n">
         <v>3324</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" ht="14.45" customHeight="1">
+    <row r="334">
       <c r="B334" t="n">
         <v>3325</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" ht="14.45" customHeight="1">
+    <row r="335">
       <c r="B335" t="n">
         <v>3326</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" ht="14.45" customHeight="1">
+    <row r="336">
       <c r="B336" t="n">
         <v>3327</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" ht="14.45" customHeight="1">
+    <row r="337">
       <c r="B337" t="n">
         <v>3328</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" ht="14.45" customHeight="1">
+    <row r="338">
       <c r="B338" t="n">
         <v>3329</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" ht="14.45" customHeight="1">
+    <row r="339">
       <c r="B339" t="n">
         <v>3330</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" ht="14.45" customHeight="1">
+    <row r="340">
       <c r="B340" t="n">
         <v>3331</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" ht="14.45" customHeight="1">
+    <row r="341">
       <c r="B341" t="n">
         <v>3332</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" ht="14.45" customHeight="1">
+    <row r="342">
       <c r="B342" t="n">
         <v>3333</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" ht="14.45" customHeight="1">
+    <row r="343">
       <c r="B343" t="n">
         <v>3334</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" ht="14.45" customHeight="1">
+    <row r="344">
       <c r="B344" t="n">
         <v>3335</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" ht="14.45" customHeight="1">
+    <row r="345">
       <c r="B345" t="n">
         <v>3336</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" ht="14.45" customHeight="1">
+    <row r="346">
       <c r="B346" t="n">
         <v>3337</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" ht="14.45" customHeight="1">
+    <row r="347">
       <c r="B347" t="n">
         <v>3338</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" ht="14.45" customHeight="1">
+    <row r="348">
       <c r="B348" t="n">
         <v>3339</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" ht="14.45" customHeight="1">
+    <row r="349">
       <c r="B349" t="n">
         <v>3340</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" ht="14.45" customHeight="1">
+    <row r="350">
       <c r="B350" t="n">
         <v>3341</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" ht="14.45" customHeight="1">
+    <row r="351">
       <c r="B351" t="n">
         <v>3342</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" ht="14.45" customHeight="1">
+    <row r="352">
       <c r="B352" t="n">
         <v>3343</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" ht="14.45" customHeight="1">
+    <row r="353">
       <c r="B353" t="n">
         <v>3344</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" ht="14.45" customHeight="1">
+    <row r="354">
       <c r="B354" t="n">
         <v>3345</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" ht="14.45" customHeight="1">
+    <row r="355">
       <c r="B355" t="n">
         <v>3346</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" ht="14.45" customHeight="1">
+    <row r="356">
       <c r="B356" t="n">
         <v>3347</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" ht="14.45" customHeight="1">
+    <row r="357">
       <c r="B357" t="n">
         <v>3348</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" ht="14.45" customHeight="1">
+    <row r="358">
       <c r="B358" t="n">
         <v>3349</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" ht="14.45" customHeight="1">
+    <row r="359">
       <c r="B359" t="n">
         <v>3350</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" ht="14.45" customHeight="1">
+    <row r="360">
       <c r="B360" t="n">
         <v>3351</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" ht="14.45" customHeight="1">
+    <row r="361">
       <c r="B361" t="n">
         <v>3352</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" ht="14.45" customHeight="1">
+    <row r="362">
       <c r="B362" t="n">
         <v>3353</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" ht="14.45" customHeight="1">
+    <row r="363">
       <c r="B363" t="n">
         <v>3354</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" ht="14.45" customHeight="1">
+    <row r="364">
       <c r="B364" t="n">
         <v>3355</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" ht="14.45" customHeight="1">
+    <row r="365">
       <c r="B365" t="n">
         <v>3356</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" ht="14.45" customHeight="1">
+    <row r="366">
       <c r="A366" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -7534,7 +7506,7 @@
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" ht="14.45" customHeight="1">
+    <row r="367">
       <c r="A367" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -7591,7 +7563,7 @@
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" ht="14.45" customHeight="1">
+    <row r="368">
       <c r="A368" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -7648,1071 +7620,1071 @@
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" ht="14.45" customHeight="1">
+    <row r="369">
       <c r="B369" t="n">
         <v>3360</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" ht="14.45" customHeight="1">
+    <row r="370">
       <c r="B370" t="n">
         <v>3361</v>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" ht="14.45" customHeight="1">
+    <row r="371">
       <c r="B371" t="n">
         <v>3362</v>
       </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" ht="14.45" customHeight="1">
+    <row r="372">
       <c r="B372" t="n">
         <v>3363</v>
       </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" ht="14.45" customHeight="1">
+    <row r="373">
       <c r="B373" t="n">
         <v>3364</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" ht="14.45" customHeight="1">
+    <row r="374">
       <c r="B374" t="n">
         <v>3365</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" ht="14.45" customHeight="1">
+    <row r="375">
       <c r="B375" t="n">
         <v>3366</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" ht="14.45" customHeight="1">
+    <row r="376">
       <c r="B376" t="n">
         <v>3367</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" ht="14.45" customHeight="1">
+    <row r="377">
       <c r="B377" t="n">
         <v>3368</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" ht="14.45" customHeight="1">
+    <row r="378">
       <c r="B378" t="n">
         <v>3369</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" ht="14.45" customHeight="1">
+    <row r="379">
       <c r="B379" t="n">
         <v>3370</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" ht="14.45" customHeight="1">
+    <row r="380">
       <c r="B380" t="n">
         <v>3371</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" ht="14.45" customHeight="1">
+    <row r="381">
       <c r="B381" t="n">
         <v>3372</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" ht="14.45" customHeight="1">
+    <row r="382">
       <c r="B382" t="n">
         <v>3373</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" ht="14.45" customHeight="1">
+    <row r="383">
       <c r="B383" t="n">
         <v>3374</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" ht="14.45" customHeight="1">
+    <row r="384">
       <c r="B384" t="n">
         <v>3375</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" ht="14.45" customHeight="1">
+    <row r="385">
       <c r="B385" t="n">
         <v>3376</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" ht="14.45" customHeight="1">
+    <row r="386">
       <c r="B386" t="n">
         <v>3377</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" ht="14.45" customHeight="1">
+    <row r="387">
       <c r="B387" t="n">
         <v>3378</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" ht="14.45" customHeight="1">
+    <row r="388">
       <c r="B388" t="n">
         <v>3379</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" ht="14.45" customHeight="1">
+    <row r="389">
       <c r="B389" t="n">
         <v>3380</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" ht="14.45" customHeight="1">
+    <row r="390">
       <c r="B390" t="n">
         <v>3381</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" ht="14.45" customHeight="1">
+    <row r="391">
       <c r="B391" t="n">
         <v>3382</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" ht="14.45" customHeight="1">
+    <row r="392">
       <c r="B392" t="n">
         <v>3383</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" ht="14.45" customHeight="1">
+    <row r="393">
       <c r="B393" t="n">
         <v>3384</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" ht="14.45" customHeight="1">
+    <row r="394">
       <c r="B394" t="n">
         <v>3385</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" ht="14.45" customHeight="1">
+    <row r="395">
       <c r="B395" t="n">
         <v>3386</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" ht="14.45" customHeight="1">
+    <row r="396">
       <c r="B396" t="n">
         <v>3387</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" ht="14.45" customHeight="1">
+    <row r="397">
       <c r="B397" t="n">
         <v>3388</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" ht="14.45" customHeight="1">
+    <row r="398">
       <c r="B398" t="n">
         <v>3389</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" ht="14.45" customHeight="1">
+    <row r="399">
       <c r="B399" t="n">
         <v>3390</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" ht="14.45" customHeight="1">
+    <row r="400">
       <c r="B400" t="n">
         <v>3391</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" ht="14.45" customHeight="1">
+    <row r="401">
       <c r="B401" t="n">
         <v>3392</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" ht="14.45" customHeight="1">
+    <row r="402">
       <c r="B402" t="n">
         <v>3393</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" ht="14.45" customHeight="1">
+    <row r="403">
       <c r="B403" t="n">
         <v>3394</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" ht="14.45" customHeight="1">
+    <row r="404">
       <c r="B404" t="n">
         <v>3395</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" ht="14.45" customHeight="1">
+    <row r="405">
       <c r="B405" t="n">
         <v>3396</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" ht="14.45" customHeight="1">
+    <row r="406">
       <c r="B406" t="n">
         <v>3397</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" ht="14.45" customHeight="1">
+    <row r="407">
       <c r="B407" t="n">
         <v>3398</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" ht="14.45" customHeight="1">
+    <row r="408">
       <c r="B408" t="n">
         <v>3399</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" ht="14.45" customHeight="1">
+    <row r="409">
       <c r="B409" t="n">
         <v>3400</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" ht="14.45" customHeight="1">
+    <row r="410">
       <c r="B410" t="n">
         <v>3401</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" ht="14.45" customHeight="1">
+    <row r="411">
       <c r="B411" t="n">
         <v>3402</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" ht="14.45" customHeight="1">
+    <row r="412">
       <c r="B412" t="n">
         <v>3403</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" ht="14.45" customHeight="1">
+    <row r="413">
       <c r="B413" t="n">
         <v>3404</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" ht="14.45" customHeight="1">
+    <row r="414">
       <c r="B414" t="n">
         <v>3405</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" ht="14.45" customHeight="1">
+    <row r="415">
       <c r="B415" t="n">
         <v>3406</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" ht="14.45" customHeight="1">
+    <row r="416">
       <c r="B416" t="n">
         <v>3407</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" ht="14.45" customHeight="1">
+    <row r="417">
       <c r="B417" t="n">
         <v>3408</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" ht="14.45" customHeight="1">
+    <row r="418">
       <c r="B418" t="n">
         <v>3409</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" ht="14.45" customHeight="1">
+    <row r="419">
       <c r="B419" t="n">
         <v>3410</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" ht="14.45" customHeight="1">
+    <row r="420">
       <c r="B420" t="n">
         <v>3411</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" ht="14.45" customHeight="1">
+    <row r="421">
       <c r="B421" t="n">
         <v>3412</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" ht="14.45" customHeight="1">
+    <row r="422">
       <c r="B422" t="n">
         <v>3413</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" ht="14.45" customHeight="1">
+    <row r="423">
       <c r="B423" t="n">
         <v>3414</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" ht="14.45" customHeight="1">
+    <row r="424">
       <c r="B424" t="n">
         <v>3415</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" ht="14.45" customHeight="1">
+    <row r="425">
       <c r="B425" t="n">
         <v>3416</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" ht="14.45" customHeight="1">
+    <row r="426">
       <c r="B426" t="n">
         <v>3417</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" ht="14.45" customHeight="1">
+    <row r="427">
       <c r="B427" t="n">
         <v>3418</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" ht="14.45" customHeight="1">
+    <row r="428">
       <c r="B428" t="n">
         <v>3419</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" ht="14.45" customHeight="1">
+    <row r="429">
       <c r="B429" t="n">
         <v>3420</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" ht="14.45" customHeight="1">
+    <row r="430">
       <c r="B430" t="n">
         <v>3421</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" ht="14.45" customHeight="1">
+    <row r="431">
       <c r="B431" t="n">
         <v>3422</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" ht="14.45" customHeight="1">
+    <row r="432">
       <c r="B432" t="n">
         <v>3423</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" ht="14.45" customHeight="1">
+    <row r="433">
       <c r="B433" t="n">
         <v>3424</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" ht="14.45" customHeight="1">
+    <row r="434">
       <c r="B434" t="n">
         <v>3425</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" ht="14.45" customHeight="1">
+    <row r="435">
       <c r="B435" t="n">
         <v>3426</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" ht="14.45" customHeight="1">
+    <row r="436">
       <c r="B436" t="n">
         <v>3427</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" ht="14.45" customHeight="1">
+    <row r="437">
       <c r="B437" t="n">
         <v>3428</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" ht="14.45" customHeight="1">
+    <row r="438">
       <c r="B438" t="n">
         <v>3429</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" ht="14.45" customHeight="1">
+    <row r="439">
       <c r="B439" t="n">
         <v>3430</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" ht="14.45" customHeight="1">
+    <row r="440">
       <c r="B440" t="n">
         <v>3431</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" ht="14.45" customHeight="1">
+    <row r="441">
       <c r="B441" t="n">
         <v>3432</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" ht="14.45" customHeight="1">
+    <row r="442">
       <c r="B442" t="n">
         <v>3433</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" ht="14.45" customHeight="1">
+    <row r="443">
       <c r="B443" t="n">
         <v>3434</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" ht="14.45" customHeight="1">
+    <row r="444">
       <c r="B444" t="n">
         <v>3435</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" ht="14.45" customHeight="1">
+    <row r="445">
       <c r="B445" t="n">
         <v>3436</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" ht="14.45" customHeight="1">
+    <row r="446">
       <c r="B446" t="n">
         <v>3437</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" ht="14.45" customHeight="1">
+    <row r="447">
       <c r="B447" t="n">
         <v>3438</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" ht="14.45" customHeight="1">
+    <row r="448">
       <c r="B448" t="n">
         <v>3439</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" ht="14.45" customHeight="1">
+    <row r="449">
       <c r="B449" t="n">
         <v>3440</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" ht="14.45" customHeight="1">
+    <row r="450">
       <c r="B450" t="n">
         <v>3441</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" ht="14.45" customHeight="1">
+    <row r="451">
       <c r="B451" t="n">
         <v>3442</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" ht="14.45" customHeight="1">
+    <row r="452">
       <c r="B452" t="n">
         <v>3443</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" ht="14.45" customHeight="1">
+    <row r="453">
       <c r="B453" t="n">
         <v>3444</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" ht="14.45" customHeight="1">
+    <row r="454">
       <c r="B454" t="n">
         <v>3445</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" ht="14.45" customHeight="1">
+    <row r="455">
       <c r="B455" t="n">
         <v>3446</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" ht="14.45" customHeight="1">
+    <row r="456">
       <c r="B456" t="n">
         <v>3447</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" ht="14.45" customHeight="1">
+    <row r="457">
       <c r="B457" t="n">
         <v>3448</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" ht="14.45" customHeight="1">
+    <row r="458">
       <c r="B458" t="n">
         <v>3449</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" ht="14.45" customHeight="1">
+    <row r="459">
       <c r="B459" t="n">
         <v>3450</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" ht="14.45" customHeight="1">
+    <row r="460">
       <c r="B460" t="n">
         <v>3451</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" ht="14.45" customHeight="1">
+    <row r="461">
       <c r="B461" t="n">
         <v>3452</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" ht="14.45" customHeight="1">
+    <row r="462">
       <c r="B462" t="n">
         <v>3453</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" ht="14.45" customHeight="1">
+    <row r="463">
       <c r="B463" t="n">
         <v>3454</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" ht="14.45" customHeight="1">
+    <row r="464">
       <c r="B464" t="n">
         <v>3455</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" ht="14.45" customHeight="1">
+    <row r="465">
       <c r="B465" t="n">
         <v>3456</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" ht="14.45" customHeight="1">
+    <row r="466">
       <c r="B466" t="n">
         <v>3457</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" ht="14.45" customHeight="1">
+    <row r="467">
       <c r="B467" t="n">
         <v>3458</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" ht="14.45" customHeight="1">
+    <row r="468">
       <c r="B468" t="n">
         <v>3459</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" ht="14.45" customHeight="1">
+    <row r="469">
       <c r="B469" t="n">
         <v>3460</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" ht="14.45" customHeight="1">
+    <row r="470">
       <c r="B470" t="n">
         <v>3461</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" ht="14.45" customHeight="1">
+    <row r="471">
       <c r="B471" t="n">
         <v>3462</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" ht="14.45" customHeight="1">
+    <row r="472">
       <c r="B472" t="n">
         <v>3463</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" ht="14.45" customHeight="1">
+    <row r="473">
       <c r="B473" t="n">
         <v>3464</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" ht="14.45" customHeight="1">
+    <row r="474">
       <c r="B474" t="n">
         <v>3465</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" ht="14.45" customHeight="1">
+    <row r="475">
       <c r="B475" t="n">
         <v>3466</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" ht="14.45" customHeight="1">
+    <row r="476">
       <c r="B476" t="n">
         <v>3467</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" ht="14.45" customHeight="1">
+    <row r="477">
       <c r="B477" t="n">
         <v>3468</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" ht="14.45" customHeight="1">
+    <row r="478">
       <c r="B478" t="n">
         <v>3469</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" ht="14.45" customHeight="1">
+    <row r="479">
       <c r="B479" t="n">
         <v>3470</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" ht="14.45" customHeight="1">
+    <row r="480">
       <c r="B480" t="n">
         <v>3471</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" ht="14.45" customHeight="1">
+    <row r="481">
       <c r="B481" t="n">
         <v>3472</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" ht="14.45" customHeight="1">
+    <row r="482">
       <c r="B482" t="n">
         <v>3473</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" ht="14.45" customHeight="1">
+    <row r="483">
       <c r="B483" t="n">
         <v>3474</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" ht="14.45" customHeight="1">
+    <row r="484">
       <c r="B484" t="n">
         <v>3475</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" ht="14.45" customHeight="1">
+    <row r="485">
       <c r="B485" t="n">
         <v>3476</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" ht="14.45" customHeight="1">
+    <row r="486">
       <c r="B486" t="n">
         <v>3477</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" ht="14.45" customHeight="1">
+    <row r="487">
       <c r="B487" t="n">
         <v>3478</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" ht="14.45" customHeight="1">
+    <row r="488">
       <c r="B488" t="n">
         <v>3479</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" ht="14.45" customHeight="1">
+    <row r="489">
       <c r="B489" t="n">
         <v>3480</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" ht="14.45" customHeight="1">
+    <row r="490">
       <c r="B490" t="n">
         <v>3481</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" ht="14.45" customHeight="1">
+    <row r="491">
       <c r="B491" t="n">
         <v>3482</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" ht="14.45" customHeight="1">
+    <row r="492">
       <c r="B492" t="n">
         <v>3483</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" ht="14.45" customHeight="1">
+    <row r="493">
       <c r="B493" t="n">
         <v>3484</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" ht="14.45" customHeight="1">
+    <row r="494">
       <c r="B494" t="n">
         <v>3485</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" ht="14.45" customHeight="1">
+    <row r="495">
       <c r="B495" t="n">
         <v>3486</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" ht="14.45" customHeight="1">
+    <row r="496">
       <c r="B496" t="n">
         <v>3487</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" ht="14.45" customHeight="1">
+    <row r="497">
       <c r="B497" t="n">
         <v>3488</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" ht="14.45" customHeight="1">
+    <row r="498">
       <c r="B498" t="n">
         <v>3489</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" ht="14.45" customHeight="1">
+    <row r="499">
       <c r="B499" t="n">
         <v>3490</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" ht="14.45" customHeight="1">
+    <row r="500">
       <c r="B500" t="n">
         <v>3491</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" ht="14.45" customHeight="1">
+    <row r="501">
       <c r="B501" t="n">
         <v>3492</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" ht="14.45" customHeight="1">
+    <row r="502">
       <c r="B502" t="n">
         <v>3493</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" ht="14.45" customHeight="1">
+    <row r="503">
       <c r="B503" t="n">
         <v>3494</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" ht="14.45" customHeight="1">
+    <row r="504">
       <c r="B504" t="n">
         <v>3495</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" ht="14.45" customHeight="1">
+    <row r="505">
       <c r="B505" t="n">
         <v>3496</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" ht="14.45" customHeight="1">
+    <row r="506">
       <c r="B506" t="n">
         <v>3497</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" ht="14.45" customHeight="1">
+    <row r="507">
       <c r="B507" t="n">
         <v>3498</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" ht="14.45" customHeight="1">
+    <row r="508">
       <c r="B508" t="n">
         <v>3499</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" ht="14.45" customHeight="1">
+    <row r="509">
       <c r="B509" t="n">
         <v>3500</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" ht="14.45" customHeight="1">
+    <row r="510">
       <c r="B510" t="n">
         <v>3501</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" ht="14.45" customHeight="1">
+    <row r="511">
       <c r="B511" t="n">
         <v>3502</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" ht="14.45" customHeight="1">
+    <row r="512">
       <c r="B512" t="n">
         <v>3503</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" ht="14.45" customHeight="1">
+    <row r="513">
       <c r="B513" t="n">
         <v>3504</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" ht="14.45" customHeight="1">
+    <row r="514">
       <c r="B514" t="n">
         <v>3505</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" ht="14.45" customHeight="1">
+    <row r="515">
       <c r="B515" t="n">
         <v>3506</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" ht="14.45" customHeight="1">
+    <row r="516">
       <c r="B516" t="n">
         <v>3507</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" ht="14.45" customHeight="1">
+    <row r="517">
       <c r="B517" t="n">
         <v>3508</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" ht="14.45" customHeight="1">
+    <row r="518">
       <c r="B518" t="n">
         <v>3509</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" ht="14.45" customHeight="1">
+    <row r="519">
       <c r="B519" t="n">
         <v>3510</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" ht="14.45" customHeight="1">
+    <row r="520">
       <c r="B520" t="n">
         <v>3511</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" ht="14.45" customHeight="1">
+    <row r="521">
       <c r="B521" t="n">
         <v>3512</v>
       </c>
@@ -8797,33 +8769,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B539"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" display="brandon.conner@gxo.com" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" display="brandon.conner@gxo.com" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" display="brandon.conner@gxo.com" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" display="brandon.conner@gxo.com" r:id="rId22"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -5462,8 +5462,18 @@
       <c r="Q81" s="4" t="n"/>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>US ,EU,</t>
+        </is>
+      </c>
       <c r="B82" t="n">
         <v>3073</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Halo</t>
+        </is>
       </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -3252,9 +3252,14 @@
           <t>NP37</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BY Case: 05803530</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OMS</t>
+          <t>OHM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4767,6 +4772,11 @@
       <c r="D64" t="inlineStr">
         <is>
           <t>NP38</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BY case 05803539</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PROJECT Bolt/Moonstone</t>
+          <t>On Running</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3064,12 +3064,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PROJECT Bolt/Moonstone</t>
+          <t>On Running</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>NP43</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BY case 05804521</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4813,7 +4818,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BY Case 05787176</t>
+          <t>PR29</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PR29A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5193,6 +5203,11 @@
       <c r="D75" t="inlineStr">
         <is>
           <t>NP21</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>BY Case 05804490</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29190" yWindow="1035" windowWidth="24120" windowHeight="11940" tabRatio="600" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Info'!$B$539</definedName>
-  </definedNames>
+  <externalReferences>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </externalReferences>
+  <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -442,7 +443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -685,6 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -789,9 +791,39 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="BY FC Clients"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN529" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN529"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN531" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="B1:AN531">
+    <filterColumn colId="1" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="Affinity Petcare"/>
+        <filter val="BOL"/>
+        <filter val="Castellbisbal multi client : DEMIX"/>
+        <filter val="Columbia Sportswear Distribution SaS"/>
+        <filter val="Commscope"/>
+        <filter val="DG Beauty"/>
+        <filter val="GXO (Multi Tenant)"/>
+        <filter val="Hunkemoller"/>
+        <filter val="Nodor"/>
+        <filter val="Oh Polly"/>
+        <filter val="Passenger Clothing Limited"/>
+        <filter val="Project Phoenix Prenatal"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="39">
     <tableColumn id="1" name="Client ID"/>
     <tableColumn id="2" name="Client"/>
@@ -1142,48 +1174,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R529"/>
+  <dimension ref="A1:R531"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15.7109375" customWidth="1" min="1" max="1"/>
+    <col width="15.7109375" customWidth="1" style="140" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="126" min="2" max="2"/>
-    <col width="36.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="72.42578125" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25.85546875" customWidth="1" min="6" max="6"/>
-    <col width="15.140625" customWidth="1" min="7" max="7"/>
-    <col width="11.7109375" customWidth="1" min="8" max="8"/>
-    <col width="19.140625" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18.140625" customWidth="1" min="11" max="11"/>
-    <col width="17.5703125" customWidth="1" min="12" max="12"/>
-    <col width="35.140625" customWidth="1" min="13" max="13"/>
-    <col width="25.28515625" customWidth="1" min="14" max="14"/>
-    <col width="33.42578125" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="36.42578125" bestFit="1" customWidth="1" style="140" min="3" max="3"/>
+    <col width="72.42578125" customWidth="1" style="140" min="4" max="4"/>
+    <col width="25" customWidth="1" style="140" min="5" max="5"/>
+    <col width="25.85546875" customWidth="1" style="140" min="6" max="6"/>
+    <col width="15.140625" customWidth="1" style="140" min="7" max="7"/>
+    <col width="11.7109375" customWidth="1" style="140" min="8" max="8"/>
+    <col width="19.140625" customWidth="1" style="140" min="9" max="9"/>
+    <col width="16" customWidth="1" style="140" min="10" max="10"/>
+    <col width="18.140625" customWidth="1" style="140" min="11" max="11"/>
+    <col width="17.5703125" customWidth="1" style="140" min="12" max="12"/>
+    <col width="35.140625" customWidth="1" style="140" min="13" max="13"/>
+    <col width="25.28515625" customWidth="1" style="140" min="14" max="14"/>
+    <col width="33.42578125" customWidth="1" style="140" min="15" max="15"/>
+    <col width="50" customWidth="1" style="140" min="16" max="16"/>
     <col width="35.85546875" customWidth="1" style="4" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" style="140" min="18" max="18"/>
     <col width="27.7109375" customWidth="1" style="4" min="19" max="19"/>
-    <col width="14.7109375" customWidth="1" min="20" max="20"/>
-    <col width="12.85546875" customWidth="1" min="21" max="23"/>
-    <col width="16.28515625" customWidth="1" min="24" max="24"/>
-    <col width="20.140625" customWidth="1" min="25" max="25"/>
-    <col width="20.5703125" customWidth="1" min="26" max="26"/>
-    <col width="14.85546875" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="20.5703125" customWidth="1" min="29" max="29"/>
-    <col width="16.140625" customWidth="1" min="30" max="30"/>
+    <col width="14.7109375" customWidth="1" style="140" min="20" max="20"/>
+    <col width="12.85546875" customWidth="1" style="140" min="21" max="23"/>
+    <col width="16.28515625" customWidth="1" style="140" min="24" max="24"/>
+    <col width="20.140625" customWidth="1" style="140" min="25" max="25"/>
+    <col width="20.5703125" customWidth="1" style="140" min="26" max="26"/>
+    <col width="14.85546875" customWidth="1" style="140" min="27" max="27"/>
+    <col width="30" customWidth="1" style="140" min="28" max="28"/>
+    <col width="20.5703125" customWidth="1" style="140" min="29" max="29"/>
+    <col width="16.140625" customWidth="1" style="140" min="30" max="30"/>
     <col width="16.140625" customWidth="1" style="53" min="31" max="31"/>
-    <col width="22.85546875" customWidth="1" min="32" max="32"/>
-    <col width="17.28515625" customWidth="1" min="33" max="33"/>
-    <col width="16.28515625" customWidth="1" style="140" min="34" max="34"/>
-    <col width="22.85546875" customWidth="1" min="35" max="36"/>
-    <col width="31.85546875" customWidth="1" min="37" max="37"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="33.28515625" customWidth="1" min="41" max="41"/>
+    <col width="22.85546875" customWidth="1" style="140" min="32" max="32"/>
+    <col width="17.28515625" customWidth="1" style="140" min="33" max="33"/>
+    <col width="16.28515625" customWidth="1" style="141" min="34" max="34"/>
+    <col width="22.85546875" customWidth="1" style="140" min="35" max="36"/>
+    <col width="31.85546875" customWidth="1" style="140" min="37" max="37"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" style="140" min="38" max="38"/>
+    <col width="33.28515625" customWidth="1" style="140" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="140">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1275,7 +1307,7 @@
         </is>
       </c>
     </row>
-    <row r="2" customFormat="1" s="62">
+    <row r="2" hidden="1" customFormat="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1359,7 +1391,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="1" s="140">
       <c r="A3" s="118" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1429,7 +1461,7 @@
       <c r="Q3" s="85" t="n"/>
       <c r="R3" s="23" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" thickBot="1">
+    <row r="4" hidden="1" ht="24" customHeight="1" s="140" thickBot="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1513,7 +1545,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="1" s="140">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1572,7 +1604,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="1" s="140">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1632,7 +1664,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" s="140">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1710,7 +1742,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" s="140">
       <c r="B8" s="27" t="n">
         <v>3007</v>
       </c>
@@ -1735,7 +1767,7 @@
       <c r="Q8" s="105" t="n"/>
       <c r="R8" s="65" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" s="140">
       <c r="B9" t="n">
         <v>3008</v>
       </c>
@@ -1818,7 +1850,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="10" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="B10" t="n">
         <v>3009</v>
       </c>
@@ -1901,7 +1933,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="11" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="11" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1981,11 +2013,11 @@
           <t>chris.menges@gxo.com</t>
         </is>
       </c>
-      <c r="R11" s="141" t="n">
+      <c r="R11" s="142" t="n">
         <v>45516</v>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" hidden="1" ht="45" customHeight="1" s="140">
       <c r="A12" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2066,7 +2098,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="13" customFormat="1" s="27">
+    <row r="13" hidden="1" customFormat="1" s="27">
       <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2130,7 +2162,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1" s="140">
       <c r="B14" s="27" t="n">
         <v>3012</v>
       </c>
@@ -2151,7 +2183,7 @@
       <c r="Q14" s="105" t="n"/>
       <c r="R14" s="65" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" hidden="1" s="140">
       <c r="B15" s="27" t="n">
         <v>3013</v>
       </c>
@@ -2172,7 +2204,7 @@
       <c r="Q15" s="105" t="n"/>
       <c r="R15" s="65" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" hidden="1" s="140">
       <c r="B16" t="n">
         <v>3014</v>
       </c>
@@ -2245,7 +2277,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="17" ht="30.75" customHeight="1" thickBot="1">
+    <row r="17" hidden="1" ht="30.75" customHeight="1" s="140" thickBot="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>Mike/Heather</t>
@@ -2309,7 +2341,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="18" ht="29.25" customFormat="1" customHeight="1" s="78">
+    <row r="18" hidden="1" ht="29.25" customFormat="1" customHeight="1" s="78">
       <c r="A18" s="78" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2398,7 +2430,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19" hidden="1" ht="48" customHeight="1" s="140">
       <c r="A19" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2476,7 +2508,7 @@
       <c r="Q19" s="85" t="n"/>
       <c r="R19" s="23" t="n"/>
     </row>
-    <row r="20" ht="45" customFormat="1" customHeight="1" s="27">
+    <row r="20" hidden="1" ht="45" customFormat="1" customHeight="1" s="27">
       <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2521,7 +2553,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="21" ht="45" customFormat="1" customHeight="1" s="27">
+    <row r="21" hidden="1" ht="45" customFormat="1" customHeight="1" s="27">
       <c r="B21" t="n">
         <v>3018</v>
       </c>
@@ -2563,7 +2595,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customFormat="1" customHeight="1" s="27">
+    <row r="22" hidden="1" ht="45" customFormat="1" customHeight="1" s="27">
       <c r="B22" t="n">
         <v>3019</v>
       </c>
@@ -2605,7 +2637,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" hidden="1" ht="45" customHeight="1" s="140">
       <c r="B23" t="n">
         <v>3020</v>
       </c>
@@ -2647,7 +2679,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="33" customFormat="1" customHeight="1" s="27">
+    <row r="24" hidden="1" ht="33" customFormat="1" customHeight="1" s="27">
       <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -2694,7 +2726,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30.75" customHeight="1">
+    <row r="25" hidden="1" ht="30.75" customHeight="1" s="140">
       <c r="B25" t="n">
         <v>3022</v>
       </c>
@@ -2769,7 +2801,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" hidden="1" ht="30" customHeight="1" s="140">
       <c r="A26" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2853,7 +2885,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" hidden="1" ht="30" customHeight="1" s="140">
       <c r="A27" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2919,7 +2951,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="45.75" customHeight="1" thickBot="1">
+    <row r="28" hidden="1" ht="45.75" customHeight="1" s="140" thickBot="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2987,7 +3019,7 @@
       </c>
       <c r="Q28" s="4" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" hidden="1" s="140">
       <c r="B29" t="n">
         <v>3026</v>
       </c>
@@ -3058,7 +3090,7 @@
       </c>
       <c r="Q29" s="4" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" hidden="1" s="140">
       <c r="B30" t="n">
         <v>3026</v>
       </c>
@@ -3100,7 +3132,7 @@
       <c r="O30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" s="140">
       <c r="A31" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3166,7 +3198,7 @@
       </c>
       <c r="O31" s="4" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" hidden="1" ht="30" customHeight="1" s="140">
       <c r="A32" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3238,7 +3270,7 @@
       </c>
       <c r="O32" s="4" t="n"/>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" hidden="1" ht="45" customHeight="1" s="140">
       <c r="A33" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3286,7 +3318,7 @@
       </c>
       <c r="O33" s="4" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" hidden="1" ht="30" customHeight="1" s="140">
       <c r="A34" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3343,7 +3375,7 @@
       </c>
       <c r="O34" s="4" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" hidden="1" ht="45" customHeight="1" s="140">
       <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3407,7 +3439,7 @@
       <c r="O35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
     </row>
-    <row r="36" ht="54" customFormat="1" customHeight="1" s="27">
+    <row r="36" hidden="1" ht="54" customFormat="1" customHeight="1" s="27">
       <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -3481,7 +3513,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" hidden="1" ht="45" customHeight="1" s="140">
       <c r="B37" t="n">
         <v>3035</v>
       </c>
@@ -3550,7 +3582,7 @@
       <c r="O37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" hidden="1" ht="60" customHeight="1" s="140">
       <c r="B38" t="n">
         <v>3035</v>
       </c>
@@ -3615,7 +3647,7 @@
       <c r="O38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
     </row>
-    <row r="39" customFormat="1" s="134">
+    <row r="39" hidden="1" customFormat="1" s="134">
       <c r="A39" s="134" t="inlineStr">
         <is>
           <t>QL</t>
@@ -3684,7 +3716,7 @@
       <c r="O39" s="136" t="n"/>
       <c r="Q39" s="136" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" hidden="1" s="140">
       <c r="B40" t="n">
         <v>3031</v>
       </c>
@@ -3751,7 +3783,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" ht="60" customHeight="1">
+    <row r="41" hidden="1" ht="60" customHeight="1" s="140">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3819,7 +3851,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="30" customHeight="1" s="140">
       <c r="A42" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3891,7 +3923,12 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" ht="45" customHeight="1">
+    <row r="43" hidden="1" ht="45.75" customHeight="1" s="140">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="B43" t="n">
         <v>3035</v>
       </c>
@@ -3935,7 +3972,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="30" customHeight="1" s="140">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4008,7 +4045,7 @@
       </c>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" hidden="1" s="140">
       <c r="A45" t="inlineStr">
         <is>
           <t>US</t>
@@ -4016,11 +4053,6 @@
       </c>
       <c r="B45" t="n">
         <v>1831</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4041,7 +4073,7 @@
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" ht="40.5" customHeight="1">
+    <row r="46" hidden="1" ht="40.5" customHeight="1" s="140">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4101,7 +4133,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="30" customHeight="1" s="140">
       <c r="A47" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4164,7 +4196,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" hidden="1" s="140">
       <c r="A48" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4221,7 +4253,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" ht="45" customHeight="1">
+    <row r="49" ht="45" customHeight="1" s="140">
       <c r="A49" t="inlineStr">
         <is>
           <t>US</t>
@@ -4265,7 +4297,7 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" customFormat="1" s="134">
+    <row r="50" hidden="1" customFormat="1" s="134">
       <c r="A50" s="134" t="inlineStr">
         <is>
           <t>QL</t>
@@ -4334,7 +4366,7 @@
       <c r="O50" s="136" t="n"/>
       <c r="Q50" s="136" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" hidden="1" s="140">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4361,7 +4393,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" hidden="1" s="140">
       <c r="A52" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4418,7 +4450,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" s="140">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4445,7 +4477,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" hidden="1" s="140">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4477,7 +4509,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" hidden="1" s="140">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4509,7 +4541,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" hidden="1" s="140">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4541,7 +4573,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" s="140">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4605,7 +4637,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" s="140">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4637,7 +4669,7 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" hidden="1" s="140">
       <c r="A60" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4669,7 +4701,7 @@
       <c r="O60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" hidden="1" s="140">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4701,7 +4733,7 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" hidden="1" s="140">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4733,7 +4765,7 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" hidden="1" s="140">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4765,7 +4797,7 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" hidden="1" s="140">
       <c r="B64" t="n">
         <v>3056</v>
       </c>
@@ -4797,7 +4829,7 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" ht="45" customHeight="1">
+    <row r="65" hidden="1" ht="45" customHeight="1" s="140">
       <c r="A65" t="inlineStr">
         <is>
           <t>US</t>
@@ -4846,7 +4878,7 @@
       <c r="O65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
     </row>
-    <row r="66" customFormat="1" s="134">
+    <row r="66" hidden="1" customFormat="1" s="134">
       <c r="A66" s="134" t="inlineStr">
         <is>
           <t>QL</t>
@@ -4890,7 +4922,7 @@
       <c r="O66" s="136" t="n"/>
       <c r="Q66" s="136" t="n"/>
     </row>
-    <row r="67" customFormat="1" s="134">
+    <row r="67" hidden="1" customFormat="1" s="134">
       <c r="A67" s="134" t="inlineStr">
         <is>
           <t>QL</t>
@@ -4934,7 +4966,7 @@
       <c r="O67" s="136" t="n"/>
       <c r="Q67" s="136" t="n"/>
     </row>
-    <row r="68" ht="45" customHeight="1">
+    <row r="68" ht="45" customHeight="1" s="140">
       <c r="A68" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5079,7 +5111,7 @@
       <c r="O71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
     </row>
-    <row r="72" ht="45" customHeight="1">
+    <row r="72" ht="45" customHeight="1" s="140">
       <c r="B72" t="n">
         <v>3063</v>
       </c>
@@ -5147,7 +5179,7 @@
       <c r="O73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
     </row>
-    <row r="74" ht="60" customHeight="1">
+    <row r="74" ht="60" customHeight="1" s="140">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5186,7 +5218,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" ht="45" customHeight="1">
+    <row r="75" ht="45" customHeight="1" s="140">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5230,7 +5262,7 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" ht="30" customHeight="1">
+    <row r="76" ht="30" customHeight="1" s="140">
       <c r="A76" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5302,7 +5334,7 @@
       <c r="O76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
     </row>
-    <row r="77" ht="45" customHeight="1">
+    <row r="77" hidden="1" ht="45" customHeight="1" s="140">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
@@ -5341,7 +5373,7 @@
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" hidden="1" s="140">
       <c r="A78" t="inlineStr">
         <is>
           <t>US</t>
@@ -5383,7 +5415,7 @@
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79" ht="45" customHeight="1">
+    <row r="79" hidden="1" ht="45" customHeight="1" s="140">
       <c r="A79" t="inlineStr">
         <is>
           <t>US</t>
@@ -5432,7 +5464,7 @@
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" hidden="1" s="140">
       <c r="A80" t="inlineStr">
         <is>
           <t>US</t>
@@ -5454,7 +5486,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" hidden="1" s="140">
       <c r="A81" t="inlineStr">
         <is>
           <t>US</t>
@@ -5486,10 +5518,10 @@
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" hidden="1" ht="45.75" customHeight="1" s="140">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US ,EU,</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -5497,2119 +5529,2081 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Halo</t>
+          <t>Halo (OpenAI)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BY Case 05808098</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>0207 Veterans Dr.
+Avon, IN 46123
+USA</t>
         </is>
       </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" hidden="1" s="140">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B83" t="n">
-        <v>3074</v>
+        <v>3073</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Halo (OpenAI)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BY Case 05808234</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
       </c>
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" hidden="1" s="140">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ASIA</t>
+        </is>
+      </c>
       <c r="B84" t="n">
-        <v>3075</v>
+        <v>3073</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Halo (OpenAI)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" hidden="1" s="140">
       <c r="B85" t="n">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" hidden="1" s="140">
       <c r="B86" t="n">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" hidden="1" s="140">
       <c r="B87" t="n">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" hidden="1" s="140">
       <c r="B88" t="n">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" hidden="1" s="140">
       <c r="B89" t="n">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" hidden="1" s="140">
       <c r="B90" t="n">
-        <v>3081</v>
+        <v>3079</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" hidden="1" s="140">
       <c r="B91" t="n">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" hidden="1" s="140">
       <c r="B92" t="n">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" hidden="1" s="140">
       <c r="B93" t="n">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" hidden="1" s="140">
       <c r="B94" t="n">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" hidden="1" s="140">
       <c r="B95" t="n">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" hidden="1" s="140">
       <c r="B96" t="n">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" hidden="1" s="140">
       <c r="B97" t="n">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" hidden="1" s="140">
       <c r="B98" t="n">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" hidden="1" s="140">
       <c r="B99" t="n">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" hidden="1" s="140">
       <c r="B100" t="n">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" hidden="1" s="140">
       <c r="B101" t="n">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" hidden="1" s="140">
       <c r="B102" t="n">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" hidden="1" s="140">
       <c r="B103" t="n">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" hidden="1" s="140">
       <c r="B104" t="n">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" hidden="1" s="140">
       <c r="B105" t="n">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" hidden="1" s="140">
       <c r="B106" t="n">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" hidden="1" s="140">
       <c r="B107" t="n">
-        <v>3098</v>
+        <v>3096</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" hidden="1" s="140">
       <c r="B108" t="n">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" hidden="1" s="140">
       <c r="B109" t="n">
-        <v>3100</v>
+        <v>3098</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" hidden="1" s="140">
       <c r="B110" t="n">
-        <v>3101</v>
+        <v>3099</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" hidden="1" s="140">
       <c r="B111" t="n">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" hidden="1" s="140">
       <c r="B112" t="n">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" hidden="1" s="140">
       <c r="B113" t="n">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" hidden="1" s="140">
       <c r="B114" t="n">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" hidden="1" s="140">
       <c r="B115" t="n">
-        <v>3106</v>
+        <v>3104</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" hidden="1" s="140">
       <c r="B116" t="n">
-        <v>3107</v>
+        <v>3105</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" hidden="1" s="140">
       <c r="B117" t="n">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" hidden="1" s="140">
       <c r="B118" t="n">
-        <v>3109</v>
+        <v>3107</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" hidden="1" s="140">
       <c r="B119" t="n">
-        <v>3110</v>
+        <v>3108</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" hidden="1" s="140">
       <c r="B120" t="n">
-        <v>3111</v>
+        <v>3109</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" hidden="1" s="140">
       <c r="B121" t="n">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" hidden="1" s="140">
       <c r="B122" t="n">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" hidden="1" s="140">
       <c r="B123" t="n">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" hidden="1" s="140">
       <c r="B124" t="n">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" hidden="1" s="140">
       <c r="B125" t="n">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" hidden="1" s="140">
       <c r="B126" t="n">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" hidden="1" s="140">
       <c r="B127" t="n">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" hidden="1" s="140">
       <c r="B128" t="n">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" hidden="1" s="140">
       <c r="B129" t="n">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" hidden="1" s="140">
       <c r="B130" t="n">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" hidden="1" s="140">
       <c r="B131" t="n">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" hidden="1" s="140">
       <c r="B132" t="n">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" hidden="1" s="140">
       <c r="B133" t="n">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" hidden="1" s="140">
       <c r="B134" t="n">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" hidden="1" s="140">
       <c r="B135" t="n">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" hidden="1" s="140">
       <c r="B136" t="n">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" hidden="1" s="140">
       <c r="B137" t="n">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" hidden="1" s="140">
       <c r="B138" t="n">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" hidden="1" s="140">
       <c r="B139" t="n">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" hidden="1" s="140">
       <c r="B140" t="n">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" hidden="1" s="140">
       <c r="B141" t="n">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" hidden="1" s="140">
       <c r="B142" t="n">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" hidden="1" s="140">
       <c r="B143" t="n">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" hidden="1" s="140">
       <c r="B144" t="n">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" hidden="1" s="140">
       <c r="B145" t="n">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" hidden="1" s="140">
       <c r="B146" t="n">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" hidden="1" s="140">
       <c r="B147" t="n">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" hidden="1" s="140">
       <c r="B148" t="n">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" hidden="1" s="140">
       <c r="B149" t="n">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" hidden="1" s="140">
       <c r="B150" t="n">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" hidden="1" s="140">
       <c r="B151" t="n">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" hidden="1" s="140">
       <c r="B152" t="n">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" hidden="1" s="140">
       <c r="B153" t="n">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" hidden="1" s="140">
       <c r="B154" t="n">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" hidden="1" s="140">
       <c r="B155" t="n">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" hidden="1" s="140">
       <c r="B156" t="n">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" hidden="1" s="140">
       <c r="B157" t="n">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" hidden="1" s="140">
       <c r="B158" t="n">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" hidden="1" s="140">
       <c r="B159" t="n">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" hidden="1" s="140">
       <c r="B160" t="n">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" hidden="1" s="140">
       <c r="B161" t="n">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" hidden="1" s="140">
       <c r="B162" t="n">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" hidden="1" s="140">
       <c r="B163" t="n">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" hidden="1" s="140">
       <c r="B164" t="n">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" hidden="1" s="140">
       <c r="B165" t="n">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" hidden="1" s="140">
       <c r="B166" t="n">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" hidden="1" s="140">
       <c r="B167" t="n">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" hidden="1" s="140">
       <c r="B168" t="n">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" hidden="1" s="140">
       <c r="B169" t="n">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" hidden="1" s="140">
       <c r="B170" t="n">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" hidden="1" s="140">
       <c r="B171" t="n">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" hidden="1" s="140">
       <c r="B172" t="n">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" hidden="1" s="140">
       <c r="B173" t="n">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" hidden="1" s="140">
       <c r="B174" t="n">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" hidden="1" s="140">
       <c r="B175" t="n">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" hidden="1" s="140">
       <c r="B176" t="n">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" hidden="1" s="140">
       <c r="B177" t="n">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" hidden="1" s="140">
       <c r="B178" t="n">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" hidden="1" s="140">
       <c r="B179" t="n">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" hidden="1" s="140">
       <c r="B180" t="n">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" hidden="1" s="140">
       <c r="B181" t="n">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" hidden="1" s="140">
       <c r="B182" t="n">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" hidden="1" s="140">
       <c r="B183" t="n">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" hidden="1" s="140">
       <c r="B184" t="n">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" hidden="1" s="140">
       <c r="B185" t="n">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" hidden="1" s="140">
       <c r="B186" t="n">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" hidden="1" s="140">
       <c r="B187" t="n">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" hidden="1" s="140">
       <c r="B188" t="n">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" hidden="1" s="140">
       <c r="B189" t="n">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" hidden="1" s="140">
       <c r="B190" t="n">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" hidden="1" s="140">
       <c r="B191" t="n">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" hidden="1" s="140">
       <c r="B192" t="n">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" hidden="1" s="140">
       <c r="B193" t="n">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" hidden="1" s="140">
       <c r="B194" t="n">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" hidden="1" s="140">
       <c r="B195" t="n">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" hidden="1" s="140">
       <c r="B196" t="n">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" hidden="1" s="140">
       <c r="B197" t="n">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" hidden="1" s="140">
       <c r="B198" t="n">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" hidden="1" s="140">
       <c r="B199" t="n">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" hidden="1" s="140">
       <c r="B200" t="n">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" hidden="1" s="140">
       <c r="B201" t="n">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" hidden="1" s="140">
       <c r="B202" t="n">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" hidden="1" s="140">
       <c r="B203" t="n">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" hidden="1" s="140">
       <c r="B204" t="n">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" hidden="1" s="140">
       <c r="B205" t="n">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" hidden="1" s="140">
       <c r="B206" t="n">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" hidden="1" s="140">
       <c r="B207" t="n">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" hidden="1" s="140">
       <c r="B208" t="n">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" hidden="1" s="140">
       <c r="B209" t="n">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" hidden="1" s="140">
       <c r="B210" t="n">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" hidden="1" s="140">
       <c r="B211" t="n">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" hidden="1" s="140">
       <c r="B212" t="n">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" hidden="1" s="140">
       <c r="B213" t="n">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" hidden="1" s="140">
       <c r="B214" t="n">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" hidden="1" s="140">
       <c r="B215" t="n">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" hidden="1" s="140">
       <c r="B216" t="n">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" hidden="1" s="140">
       <c r="B217" t="n">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" hidden="1" s="140">
       <c r="B218" t="n">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" hidden="1" s="140">
       <c r="B219" t="n">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" hidden="1" s="140">
       <c r="B220" t="n">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" hidden="1" s="140">
       <c r="B221" t="n">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" hidden="1" s="140">
       <c r="B222" t="n">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" hidden="1" s="140">
       <c r="B223" t="n">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" hidden="1" s="140">
       <c r="B224" t="n">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" hidden="1" s="140">
       <c r="B225" t="n">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" hidden="1" s="140">
       <c r="B226" t="n">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" hidden="1" s="140">
       <c r="B227" t="n">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" hidden="1" s="140">
       <c r="B228" t="n">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" hidden="1" s="140">
       <c r="B229" t="n">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" hidden="1" s="140">
       <c r="B230" t="n">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" hidden="1" s="140">
       <c r="B231" t="n">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" hidden="1" s="140">
       <c r="B232" t="n">
-        <v>3223</v>
+        <v>3221</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" hidden="1" s="140">
       <c r="B233" t="n">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" hidden="1" s="140">
       <c r="B234" t="n">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" hidden="1" s="140">
       <c r="B235" t="n">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236">
+    <row r="236" hidden="1" s="140">
       <c r="B236" t="n">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" hidden="1" s="140">
       <c r="B237" t="n">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" hidden="1" s="140">
       <c r="B238" t="n">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" hidden="1" s="140">
       <c r="B239" t="n">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240">
+    <row r="240" hidden="1" s="140">
       <c r="B240" t="n">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" hidden="1" s="140">
       <c r="B241" t="n">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242">
+    <row r="242" hidden="1" s="140">
       <c r="B242" t="n">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" hidden="1" s="140">
       <c r="B243" t="n">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" hidden="1" s="140">
       <c r="B244" t="n">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" hidden="1" s="140">
       <c r="B245" t="n">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" hidden="1" s="140">
       <c r="B246" t="n">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" hidden="1" s="140">
       <c r="B247" t="n">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" hidden="1" s="140">
       <c r="B248" t="n">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" hidden="1" s="140">
       <c r="B249" t="n">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" hidden="1" s="140">
       <c r="B250" t="n">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" hidden="1" s="140">
       <c r="B251" t="n">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" hidden="1" s="140">
       <c r="B252" t="n">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" hidden="1" s="140">
       <c r="B253" t="n">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254">
+    <row r="254" hidden="1" s="140">
       <c r="B254" t="n">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255">
+    <row r="255" hidden="1" s="140">
       <c r="B255" t="n">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256">
+    <row r="256" hidden="1" s="140">
       <c r="B256" t="n">
-        <v>3247</v>
+        <v>3245</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257">
+    <row r="257" hidden="1" s="140">
       <c r="B257" t="n">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258">
+    <row r="258" hidden="1" s="140">
       <c r="B258" t="n">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259">
+    <row r="259" hidden="1" s="140">
       <c r="B259" t="n">
-        <v>3250</v>
+        <v>3248</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260">
+    <row r="260" hidden="1" s="140">
       <c r="B260" t="n">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261">
+    <row r="261" hidden="1" s="140">
       <c r="B261" t="n">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262">
+    <row r="262" hidden="1" s="140">
       <c r="B262" t="n">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263">
+    <row r="263" hidden="1" s="140">
       <c r="B263" t="n">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264">
+    <row r="264" hidden="1" s="140">
       <c r="B264" t="n">
-        <v>3255</v>
+        <v>3253</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265">
+    <row r="265" hidden="1" s="140">
       <c r="B265" t="n">
-        <v>3256</v>
+        <v>3254</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266">
+    <row r="266" hidden="1" s="140">
       <c r="B266" t="n">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267">
+    <row r="267" hidden="1" s="140">
       <c r="B267" t="n">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268">
+    <row r="268" hidden="1" s="140">
       <c r="B268" t="n">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269">
+    <row r="269" hidden="1" s="140">
       <c r="B269" t="n">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270">
+    <row r="270" hidden="1" s="140">
       <c r="B270" t="n">
-        <v>3261</v>
+        <v>3259</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271">
+    <row r="271" hidden="1" s="140">
       <c r="B271" t="n">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272">
+    <row r="272" hidden="1" s="140">
       <c r="B272" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273">
+    <row r="273" hidden="1" s="140">
       <c r="B273" t="n">
-        <v>3264</v>
+        <v>3262</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274">
+    <row r="274" hidden="1" s="140">
       <c r="B274" t="n">
-        <v>3265</v>
+        <v>3263</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275">
+    <row r="275" hidden="1" s="140">
       <c r="B275" t="n">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276">
+    <row r="276" hidden="1" s="140">
       <c r="B276" t="n">
-        <v>3267</v>
+        <v>3265</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277">
+    <row r="277" hidden="1" s="140">
       <c r="B277" t="n">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278">
+    <row r="278" hidden="1" s="140">
       <c r="B278" t="n">
-        <v>3269</v>
+        <v>3267</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279">
+    <row r="279" hidden="1" s="140">
       <c r="B279" t="n">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280">
+    <row r="280" hidden="1" s="140">
       <c r="B280" t="n">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281">
+    <row r="281" hidden="1" s="140">
       <c r="B281" t="n">
-        <v>3272</v>
+        <v>3270</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282">
+    <row r="282" hidden="1" s="140">
       <c r="B282" t="n">
-        <v>3273</v>
+        <v>3271</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" hidden="1" s="140">
       <c r="B283" t="n">
-        <v>3274</v>
+        <v>3272</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284">
+    <row r="284" hidden="1" s="140">
       <c r="B284" t="n">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285">
+    <row r="285" hidden="1" s="140">
       <c r="B285" t="n">
-        <v>3276</v>
+        <v>3274</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286">
+    <row r="286" hidden="1" s="140">
       <c r="B286" t="n">
-        <v>3277</v>
+        <v>3275</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287">
+    <row r="287" hidden="1" s="140">
       <c r="B287" t="n">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" hidden="1" s="140">
       <c r="B288" t="n">
-        <v>3279</v>
+        <v>3277</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" hidden="1" s="140">
       <c r="B289" t="n">
-        <v>3280</v>
+        <v>3278</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" hidden="1" s="140">
       <c r="B290" t="n">
-        <v>3281</v>
+        <v>3279</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291">
+    <row r="291" hidden="1" s="140">
       <c r="B291" t="n">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292">
+    <row r="292" hidden="1" s="140">
       <c r="B292" t="n">
-        <v>3283</v>
+        <v>3281</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293">
+    <row r="293" hidden="1" s="140">
       <c r="B293" t="n">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" hidden="1" s="140">
       <c r="B294" t="n">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295">
+    <row r="295" hidden="1" s="140">
       <c r="B295" t="n">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296">
+    <row r="296" hidden="1" s="140">
       <c r="B296" t="n">
-        <v>3287</v>
+        <v>3285</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297">
+    <row r="297" hidden="1" s="140">
       <c r="B297" t="n">
-        <v>3288</v>
+        <v>3286</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298">
+    <row r="298" hidden="1" s="140">
       <c r="B298" t="n">
-        <v>3289</v>
+        <v>3287</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299">
+    <row r="299" hidden="1" s="140">
       <c r="B299" t="n">
-        <v>3290</v>
+        <v>3288</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300">
+    <row r="300" hidden="1" s="140">
       <c r="B300" t="n">
-        <v>3291</v>
+        <v>3289</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301">
+    <row r="301" hidden="1" s="140">
       <c r="B301" t="n">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302">
+    <row r="302" hidden="1" s="140">
       <c r="B302" t="n">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303">
+    <row r="303" hidden="1" s="140">
       <c r="B303" t="n">
-        <v>3294</v>
+        <v>3292</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" hidden="1" s="140">
       <c r="B304" t="n">
-        <v>3295</v>
+        <v>3293</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305">
+    <row r="305" hidden="1" s="140">
       <c r="B305" t="n">
-        <v>3296</v>
+        <v>3294</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" hidden="1" s="140">
       <c r="B306" t="n">
-        <v>3297</v>
+        <v>3295</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" hidden="1" s="140">
       <c r="B307" t="n">
-        <v>3298</v>
+        <v>3296</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308">
+    <row r="308" hidden="1" s="140">
       <c r="B308" t="n">
-        <v>3299</v>
+        <v>3297</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" hidden="1" s="140">
       <c r="B309" t="n">
-        <v>3300</v>
+        <v>3298</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310">
+    <row r="310" hidden="1" s="140">
       <c r="B310" t="n">
-        <v>3301</v>
+        <v>3299</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311">
+    <row r="311" hidden="1" s="140">
       <c r="B311" t="n">
-        <v>3302</v>
+        <v>3300</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312">
+    <row r="312" hidden="1" s="140">
       <c r="B312" t="n">
-        <v>3303</v>
+        <v>3301</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313">
+    <row r="313" hidden="1" s="140">
       <c r="B313" t="n">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314">
+    <row r="314" hidden="1" s="140">
       <c r="B314" t="n">
-        <v>3305</v>
+        <v>3303</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315">
+    <row r="315" hidden="1" s="140">
       <c r="B315" t="n">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316">
+    <row r="316" hidden="1" s="140">
       <c r="B316" t="n">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317">
+    <row r="317" hidden="1" s="140">
       <c r="B317" t="n">
-        <v>3308</v>
+        <v>3306</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318">
+    <row r="318" hidden="1" s="140">
       <c r="B318" t="n">
-        <v>3309</v>
+        <v>3307</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319">
+    <row r="319" hidden="1" s="140">
       <c r="B319" t="n">
-        <v>3310</v>
+        <v>3308</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320">
+    <row r="320" hidden="1" s="140">
       <c r="B320" t="n">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321">
+    <row r="321" hidden="1" s="140">
       <c r="B321" t="n">
-        <v>3312</v>
+        <v>3310</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322">
+    <row r="322" hidden="1" s="140">
       <c r="B322" t="n">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323">
+    <row r="323" hidden="1" s="140">
       <c r="B323" t="n">
-        <v>3314</v>
+        <v>3312</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324">
+    <row r="324" hidden="1" s="140">
       <c r="B324" t="n">
-        <v>3315</v>
+        <v>3313</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325">
+    <row r="325" hidden="1" s="140">
       <c r="B325" t="n">
-        <v>3316</v>
+        <v>3314</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326">
+    <row r="326" hidden="1" s="140">
       <c r="B326" t="n">
-        <v>3317</v>
+        <v>3315</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327">
+    <row r="327" hidden="1" s="140">
       <c r="B327" t="n">
-        <v>3318</v>
+        <v>3316</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328">
+    <row r="328" hidden="1" s="140">
       <c r="B328" t="n">
-        <v>3319</v>
+        <v>3317</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329">
+    <row r="329" hidden="1" s="140">
       <c r="B329" t="n">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330">
+    <row r="330" hidden="1" s="140">
       <c r="B330" t="n">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331">
+    <row r="331" hidden="1" s="140">
       <c r="B331" t="n">
-        <v>3322</v>
+        <v>3320</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332">
+    <row r="332" hidden="1" s="140">
       <c r="B332" t="n">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333">
+    <row r="333" hidden="1" s="140">
       <c r="B333" t="n">
-        <v>3324</v>
+        <v>3322</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334">
+    <row r="334" hidden="1" s="140">
       <c r="B334" t="n">
-        <v>3325</v>
+        <v>3323</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335">
+    <row r="335" hidden="1" s="140">
       <c r="B335" t="n">
-        <v>3326</v>
+        <v>3324</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336">
+    <row r="336" hidden="1" s="140">
       <c r="B336" t="n">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337">
+    <row r="337" hidden="1" s="140">
       <c r="B337" t="n">
-        <v>3328</v>
+        <v>3326</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338">
+    <row r="338" hidden="1" s="140">
       <c r="B338" t="n">
-        <v>3329</v>
+        <v>3327</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339">
+    <row r="339" hidden="1" s="140">
       <c r="B339" t="n">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340">
+    <row r="340" hidden="1" s="140">
       <c r="B340" t="n">
-        <v>3331</v>
+        <v>3329</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341">
+    <row r="341" hidden="1" s="140">
       <c r="B341" t="n">
-        <v>3332</v>
+        <v>3330</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342">
+    <row r="342" hidden="1" s="140">
       <c r="B342" t="n">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343">
+    <row r="343" hidden="1" s="140">
       <c r="B343" t="n">
-        <v>3334</v>
+        <v>3332</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344">
+    <row r="344" hidden="1" s="140">
       <c r="B344" t="n">
-        <v>3335</v>
+        <v>3333</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345">
+    <row r="345" hidden="1" s="140">
       <c r="B345" t="n">
-        <v>3336</v>
+        <v>3334</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346">
+    <row r="346" hidden="1" s="140">
       <c r="B346" t="n">
-        <v>3337</v>
+        <v>3335</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347">
+    <row r="347" hidden="1" s="140">
       <c r="B347" t="n">
-        <v>3338</v>
+        <v>3336</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348">
+    <row r="348" hidden="1" s="140">
       <c r="B348" t="n">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349">
+    <row r="349" hidden="1" s="140">
       <c r="B349" t="n">
-        <v>3340</v>
+        <v>3338</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350">
+    <row r="350" hidden="1" s="140">
       <c r="B350" t="n">
-        <v>3341</v>
+        <v>3339</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351">
+    <row r="351" hidden="1" s="140">
       <c r="B351" t="n">
-        <v>3342</v>
+        <v>3340</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352">
+    <row r="352" hidden="1" s="140">
       <c r="B352" t="n">
-        <v>3343</v>
+        <v>3341</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353">
+    <row r="353" hidden="1" s="140">
       <c r="B353" t="n">
-        <v>3344</v>
+        <v>3342</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354">
+    <row r="354" hidden="1" s="140">
       <c r="B354" t="n">
-        <v>3345</v>
+        <v>3343</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355">
+    <row r="355" hidden="1" s="140">
       <c r="B355" t="n">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356">
+    <row r="356" hidden="1" s="140">
       <c r="B356" t="n">
-        <v>3347</v>
+        <v>3345</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" hidden="1" s="140">
       <c r="B357" t="n">
-        <v>3348</v>
+        <v>3346</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358">
+    <row r="358" hidden="1" s="140">
       <c r="B358" t="n">
-        <v>3349</v>
+        <v>3347</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359">
+    <row r="359" hidden="1" s="140">
       <c r="B359" t="n">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360">
+    <row r="360" hidden="1" s="140">
       <c r="B360" t="n">
-        <v>3351</v>
+        <v>3349</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361">
+    <row r="361" hidden="1" s="140">
       <c r="B361" t="n">
-        <v>3352</v>
+        <v>3350</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362">
+    <row r="362" hidden="1" s="140">
       <c r="B362" t="n">
-        <v>3353</v>
+        <v>3351</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363">
+    <row r="363" hidden="1" s="140">
       <c r="B363" t="n">
-        <v>3354</v>
+        <v>3352</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364">
+    <row r="364" hidden="1" s="140">
       <c r="B364" t="n">
-        <v>3355</v>
+        <v>3353</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365">
+    <row r="365" hidden="1" s="140">
       <c r="B365" t="n">
-        <v>3356</v>
+        <v>3354</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="366" hidden="1" s="140">
       <c r="B366" t="n">
-        <v>3357</v>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>Unilever FOOD</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>NP8</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>FEG</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>bh10-00j-euw</t>
-        </is>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
+        <v>3355</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="367" hidden="1" s="140">
       <c r="B367" t="n">
-        <v>3358</v>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>Unilever HOME CARE</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>NP8</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>FEG</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>bh10-00j-euw</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
+        <v>3356</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368">
+    <row r="368" hidden="1" s="140">
       <c r="A368" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>3359</v>
+        <v>3357</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unilever Personal Care</t>
+          <t>Unilever FOOD</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -7655,1109 +7649,1202 @@
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369">
+    <row r="369" hidden="1" s="140">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B369" t="n">
-        <v>3360</v>
+        <v>3358</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Unilever HOME CARE</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370">
+    <row r="370" hidden="1" s="140">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B370" t="n">
-        <v>3361</v>
+        <v>3359</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Unilever Personal Care</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371">
+    <row r="371" hidden="1" s="140">
       <c r="B371" t="n">
-        <v>3362</v>
+        <v>3360</v>
       </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372">
+    <row r="372" hidden="1" s="140">
       <c r="B372" t="n">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373">
+    <row r="373" hidden="1" s="140">
       <c r="B373" t="n">
-        <v>3364</v>
+        <v>3362</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374">
+    <row r="374" hidden="1" s="140">
       <c r="B374" t="n">
-        <v>3365</v>
+        <v>3363</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375">
+    <row r="375" hidden="1" s="140">
       <c r="B375" t="n">
-        <v>3366</v>
+        <v>3364</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376">
+    <row r="376" hidden="1" s="140">
       <c r="B376" t="n">
-        <v>3367</v>
+        <v>3365</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377">
+    <row r="377" hidden="1" s="140">
       <c r="B377" t="n">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" hidden="1" s="140">
       <c r="B378" t="n">
-        <v>3369</v>
+        <v>3367</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379">
+    <row r="379" hidden="1" s="140">
       <c r="B379" t="n">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380">
+    <row r="380" hidden="1" s="140">
       <c r="B380" t="n">
-        <v>3371</v>
+        <v>3369</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381">
+    <row r="381" hidden="1" s="140">
       <c r="B381" t="n">
-        <v>3372</v>
+        <v>3370</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382">
+    <row r="382" hidden="1" s="140">
       <c r="B382" t="n">
-        <v>3373</v>
+        <v>3371</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383">
+    <row r="383" hidden="1" s="140">
       <c r="B383" t="n">
-        <v>3374</v>
+        <v>3372</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384">
+    <row r="384" hidden="1" s="140">
       <c r="B384" t="n">
-        <v>3375</v>
+        <v>3373</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385">
+    <row r="385" hidden="1" s="140">
       <c r="B385" t="n">
-        <v>3376</v>
+        <v>3374</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386">
+    <row r="386" hidden="1" s="140">
       <c r="B386" t="n">
-        <v>3377</v>
+        <v>3375</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" hidden="1" s="140">
       <c r="B387" t="n">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388">
+    <row r="388" hidden="1" s="140">
       <c r="B388" t="n">
-        <v>3379</v>
+        <v>3377</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389">
+    <row r="389" hidden="1" s="140">
       <c r="B389" t="n">
-        <v>3380</v>
+        <v>3378</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390">
+    <row r="390" hidden="1" s="140">
       <c r="B390" t="n">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391">
+    <row r="391" hidden="1" s="140">
       <c r="B391" t="n">
-        <v>3382</v>
+        <v>3380</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392">
+    <row r="392" hidden="1" s="140">
       <c r="B392" t="n">
-        <v>3383</v>
+        <v>3381</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393">
+    <row r="393" hidden="1" s="140">
       <c r="B393" t="n">
-        <v>3384</v>
+        <v>3382</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394">
+    <row r="394" hidden="1" s="140">
       <c r="B394" t="n">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395">
+    <row r="395" hidden="1" s="140">
       <c r="B395" t="n">
-        <v>3386</v>
+        <v>3384</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396">
+    <row r="396" hidden="1" s="140">
       <c r="B396" t="n">
-        <v>3387</v>
+        <v>3385</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397">
+    <row r="397" hidden="1" s="140">
       <c r="B397" t="n">
-        <v>3388</v>
+        <v>3386</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398">
+    <row r="398" hidden="1" s="140">
       <c r="B398" t="n">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399">
+    <row r="399" hidden="1" s="140">
       <c r="B399" t="n">
-        <v>3390</v>
+        <v>3388</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400">
+    <row r="400" hidden="1" s="140">
       <c r="B400" t="n">
-        <v>3391</v>
+        <v>3389</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401">
+    <row r="401" hidden="1" s="140">
       <c r="B401" t="n">
-        <v>3392</v>
+        <v>3390</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402">
+    <row r="402" hidden="1" s="140">
       <c r="B402" t="n">
-        <v>3393</v>
+        <v>3391</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403">
+    <row r="403" hidden="1" s="140">
       <c r="B403" t="n">
-        <v>3394</v>
+        <v>3392</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404">
+    <row r="404" hidden="1" s="140">
       <c r="B404" t="n">
-        <v>3395</v>
+        <v>3393</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405">
+    <row r="405" hidden="1" s="140">
       <c r="B405" t="n">
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406">
+    <row r="406" hidden="1" s="140">
       <c r="B406" t="n">
-        <v>3397</v>
+        <v>3395</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407">
+    <row r="407" hidden="1" s="140">
       <c r="B407" t="n">
-        <v>3398</v>
+        <v>3396</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408">
+    <row r="408" hidden="1" s="140">
       <c r="B408" t="n">
-        <v>3399</v>
+        <v>3397</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409">
+    <row r="409" hidden="1" s="140">
       <c r="B409" t="n">
-        <v>3400</v>
+        <v>3398</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410">
+    <row r="410" hidden="1" s="140">
       <c r="B410" t="n">
-        <v>3401</v>
+        <v>3399</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411">
+    <row r="411" hidden="1" s="140">
       <c r="B411" t="n">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412">
+    <row r="412" hidden="1" s="140">
       <c r="B412" t="n">
-        <v>3403</v>
+        <v>3401</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413">
+    <row r="413" hidden="1" s="140">
       <c r="B413" t="n">
-        <v>3404</v>
+        <v>3402</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414">
+    <row r="414" hidden="1" s="140">
       <c r="B414" t="n">
-        <v>3405</v>
+        <v>3403</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415">
+    <row r="415" hidden="1" s="140">
       <c r="B415" t="n">
-        <v>3406</v>
+        <v>3404</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416">
+    <row r="416" hidden="1" s="140">
       <c r="B416" t="n">
-        <v>3407</v>
+        <v>3405</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417">
+    <row r="417" hidden="1" s="140">
       <c r="B417" t="n">
-        <v>3408</v>
+        <v>3406</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418">
+    <row r="418" hidden="1" s="140">
       <c r="B418" t="n">
-        <v>3409</v>
+        <v>3407</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419">
+    <row r="419" hidden="1" s="140">
       <c r="B419" t="n">
-        <v>3410</v>
+        <v>3408</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420">
+    <row r="420" hidden="1" s="140">
       <c r="B420" t="n">
-        <v>3411</v>
+        <v>3409</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421">
+    <row r="421" hidden="1" s="140">
       <c r="B421" t="n">
-        <v>3412</v>
+        <v>3410</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422">
+    <row r="422" hidden="1" s="140">
       <c r="B422" t="n">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423">
+    <row r="423" hidden="1" s="140">
       <c r="B423" t="n">
-        <v>3414</v>
+        <v>3412</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424">
+    <row r="424" hidden="1" s="140">
       <c r="B424" t="n">
-        <v>3415</v>
+        <v>3413</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425">
+    <row r="425" hidden="1" s="140">
       <c r="B425" t="n">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426">
+    <row r="426" hidden="1" s="140">
       <c r="B426" t="n">
-        <v>3417</v>
+        <v>3415</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427">
+    <row r="427" hidden="1" s="140">
       <c r="B427" t="n">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428">
+    <row r="428" hidden="1" s="140">
       <c r="B428" t="n">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429">
+    <row r="429" hidden="1" s="140">
       <c r="B429" t="n">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430">
+    <row r="430" hidden="1" s="140">
       <c r="B430" t="n">
-        <v>3421</v>
+        <v>3419</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431">
+    <row r="431" hidden="1" s="140">
       <c r="B431" t="n">
-        <v>3422</v>
+        <v>3420</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432">
+    <row r="432" hidden="1" s="140">
       <c r="B432" t="n">
-        <v>3423</v>
+        <v>3421</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433">
+    <row r="433" hidden="1" s="140">
       <c r="B433" t="n">
-        <v>3424</v>
+        <v>3422</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434">
+    <row r="434" hidden="1" s="140">
       <c r="B434" t="n">
-        <v>3425</v>
+        <v>3423</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435">
+    <row r="435" hidden="1" s="140">
       <c r="B435" t="n">
-        <v>3426</v>
+        <v>3424</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436">
+    <row r="436" hidden="1" s="140">
       <c r="B436" t="n">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" hidden="1" s="140">
       <c r="B437" t="n">
-        <v>3428</v>
+        <v>3426</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438">
+    <row r="438" hidden="1" s="140">
       <c r="B438" t="n">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439">
+    <row r="439" hidden="1" s="140">
       <c r="B439" t="n">
-        <v>3430</v>
+        <v>3428</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440">
+    <row r="440" hidden="1" s="140">
       <c r="B440" t="n">
-        <v>3431</v>
+        <v>3429</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441">
+    <row r="441" hidden="1" s="140">
       <c r="B441" t="n">
-        <v>3432</v>
+        <v>3430</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442">
+    <row r="442" hidden="1" s="140">
       <c r="B442" t="n">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443">
+    <row r="443" hidden="1" s="140">
       <c r="B443" t="n">
-        <v>3434</v>
+        <v>3432</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444">
+    <row r="444" hidden="1" s="140">
       <c r="B444" t="n">
-        <v>3435</v>
+        <v>3433</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445">
+    <row r="445" hidden="1" s="140">
       <c r="B445" t="n">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446">
+    <row r="446" hidden="1" s="140">
       <c r="B446" t="n">
-        <v>3437</v>
+        <v>3435</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447">
+    <row r="447" hidden="1" s="140">
       <c r="B447" t="n">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448">
+    <row r="448" hidden="1" s="140">
       <c r="B448" t="n">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449">
+    <row r="449" hidden="1" s="140">
       <c r="B449" t="n">
-        <v>3440</v>
+        <v>3438</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450">
+    <row r="450" hidden="1" s="140">
       <c r="B450" t="n">
-        <v>3441</v>
+        <v>3439</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451">
+    <row r="451" hidden="1" s="140">
       <c r="B451" t="n">
-        <v>3442</v>
+        <v>3440</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452">
+    <row r="452" hidden="1" s="140">
       <c r="B452" t="n">
-        <v>3443</v>
+        <v>3441</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453">
+    <row r="453" hidden="1" s="140">
       <c r="B453" t="n">
-        <v>3444</v>
+        <v>3442</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454">
+    <row r="454" hidden="1" s="140">
       <c r="B454" t="n">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455">
+    <row r="455" hidden="1" s="140">
       <c r="B455" t="n">
-        <v>3446</v>
+        <v>3444</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456">
+    <row r="456" hidden="1" s="140">
       <c r="B456" t="n">
-        <v>3447</v>
+        <v>3445</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457">
+    <row r="457" hidden="1" s="140">
       <c r="B457" t="n">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458">
+    <row r="458" hidden="1" s="140">
       <c r="B458" t="n">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459">
+    <row r="459" hidden="1" s="140">
       <c r="B459" t="n">
-        <v>3450</v>
+        <v>3448</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460">
+    <row r="460" hidden="1" s="140">
       <c r="B460" t="n">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461">
+    <row r="461" hidden="1" s="140">
       <c r="B461" t="n">
-        <v>3452</v>
+        <v>3450</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462">
+    <row r="462" hidden="1" s="140">
       <c r="B462" t="n">
-        <v>3453</v>
+        <v>3451</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463">
+    <row r="463" hidden="1" s="140">
       <c r="B463" t="n">
-        <v>3454</v>
+        <v>3452</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464">
+    <row r="464" hidden="1" s="140">
       <c r="B464" t="n">
-        <v>3455</v>
+        <v>3453</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465">
+    <row r="465" hidden="1" s="140">
       <c r="B465" t="n">
-        <v>3456</v>
+        <v>3454</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466">
+    <row r="466" hidden="1" s="140">
       <c r="B466" t="n">
-        <v>3457</v>
+        <v>3455</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467">
+    <row r="467" hidden="1" s="140">
       <c r="B467" t="n">
-        <v>3458</v>
+        <v>3456</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468">
+    <row r="468" hidden="1" s="140">
       <c r="B468" t="n">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469">
+    <row r="469" hidden="1" s="140">
       <c r="B469" t="n">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470">
+    <row r="470" hidden="1" s="140">
       <c r="B470" t="n">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471">
+    <row r="471" hidden="1" s="140">
       <c r="B471" t="n">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472">
+    <row r="472" hidden="1" s="140">
       <c r="B472" t="n">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473">
+    <row r="473" hidden="1" s="140">
       <c r="B473" t="n">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474">
+    <row r="474" hidden="1" s="140">
       <c r="B474" t="n">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475">
+    <row r="475" hidden="1" s="140">
       <c r="B475" t="n">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476">
+    <row r="476" hidden="1" s="140">
       <c r="B476" t="n">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477">
+    <row r="477" hidden="1" s="140">
       <c r="B477" t="n">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478">
+    <row r="478" hidden="1" s="140">
       <c r="B478" t="n">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479">
+    <row r="479" hidden="1" s="140">
       <c r="B479" t="n">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480">
+    <row r="480" hidden="1" s="140">
       <c r="B480" t="n">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481">
+    <row r="481" hidden="1" s="140">
       <c r="B481" t="n">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482">
+    <row r="482" hidden="1" s="140">
       <c r="B482" t="n">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483">
+    <row r="483" hidden="1" s="140">
       <c r="B483" t="n">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484">
+    <row r="484" hidden="1" s="140">
       <c r="B484" t="n">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" hidden="1" s="140">
       <c r="B485" t="n">
-        <v>3476</v>
+        <v>3474</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" hidden="1" s="140">
       <c r="B486" t="n">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487">
+    <row r="487" hidden="1" s="140">
       <c r="B487" t="n">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488">
+    <row r="488" hidden="1" s="140">
       <c r="B488" t="n">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489">
+    <row r="489" hidden="1" s="140">
       <c r="B489" t="n">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490">
+    <row r="490" hidden="1" s="140">
       <c r="B490" t="n">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491">
+    <row r="491" hidden="1" s="140">
       <c r="B491" t="n">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492">
+    <row r="492" hidden="1" s="140">
       <c r="B492" t="n">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493">
+    <row r="493" hidden="1" s="140">
       <c r="B493" t="n">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494">
+    <row r="494" hidden="1" s="140">
       <c r="B494" t="n">
-        <v>3485</v>
+        <v>3483</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495">
+    <row r="495" hidden="1" s="140">
       <c r="B495" t="n">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496">
+    <row r="496" hidden="1" s="140">
       <c r="B496" t="n">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497">
+    <row r="497" hidden="1" s="140">
       <c r="B497" t="n">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" hidden="1" s="140">
       <c r="B498" t="n">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" hidden="1" s="140">
       <c r="B499" t="n">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500">
+    <row r="500" hidden="1" s="140">
       <c r="B500" t="n">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501">
+    <row r="501" hidden="1" s="140">
       <c r="B501" t="n">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502">
+    <row r="502" hidden="1" s="140">
       <c r="B502" t="n">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503">
+    <row r="503" hidden="1" s="140">
       <c r="B503" t="n">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504">
+    <row r="504" hidden="1" s="140">
       <c r="B504" t="n">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505">
+    <row r="505" hidden="1" s="140">
       <c r="B505" t="n">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506">
+    <row r="506" hidden="1" s="140">
       <c r="B506" t="n">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507">
+    <row r="507" hidden="1" s="140">
       <c r="B507" t="n">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" hidden="1" s="140">
       <c r="B508" t="n">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509">
+    <row r="509" hidden="1" s="140">
       <c r="B509" t="n">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510">
+    <row r="510" hidden="1" s="140">
       <c r="B510" t="n">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511">
+    <row r="511" hidden="1" s="140">
       <c r="B511" t="n">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512">
+    <row r="512" hidden="1" s="140">
       <c r="B512" t="n">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513">
+    <row r="513" hidden="1" s="140">
       <c r="B513" t="n">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514">
+    <row r="514" hidden="1" s="140">
       <c r="B514" t="n">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515">
+    <row r="515" hidden="1" s="140">
       <c r="B515" t="n">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516">
+    <row r="516" hidden="1" s="140">
       <c r="B516" t="n">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517">
+    <row r="517" hidden="1" s="140">
       <c r="B517" t="n">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518">
+    <row r="518" hidden="1" s="140">
       <c r="B518" t="n">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519">
+    <row r="519" hidden="1" s="140">
       <c r="B519" t="n">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520">
+    <row r="520" hidden="1" s="140">
       <c r="B520" t="n">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521">
+    <row r="521" hidden="1" s="140">
       <c r="B521" t="n">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" ht="15" customHeight="1">
+    <row r="522" hidden="1" s="140">
       <c r="B522" t="n">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" ht="15" customHeight="1">
+    <row r="523" hidden="1" s="140">
       <c r="B523" t="n">
-        <v>3514</v>
-      </c>
-      <c r="F523" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>3512</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" ht="15" customHeight="1">
+    <row r="524" hidden="1" ht="15" customHeight="1" s="140">
       <c r="B524" t="n">
-        <v>3515</v>
-      </c>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>3513</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" ht="15" customHeight="1">
+    <row r="525" hidden="1" ht="15" customHeight="1" s="140">
+      <c r="B525" t="n">
+        <v>3514</v>
+      </c>
       <c r="F525" t="inlineStr">
         <is>
           <t>A</t>
@@ -8766,7 +8853,10 @@
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" ht="15" customHeight="1">
+    <row r="526" hidden="1" ht="15" customHeight="1" s="140">
+      <c r="B526" t="n">
+        <v>3515</v>
+      </c>
       <c r="F526" t="inlineStr">
         <is>
           <t>A</t>
@@ -8775,7 +8865,7 @@
       <c r="O526" s="4" t="n"/>
       <c r="Q526" s="4" t="n"/>
     </row>
-    <row r="527" ht="15" customHeight="1">
+    <row r="527" hidden="1" ht="15" customHeight="1" s="140">
       <c r="F527" t="inlineStr">
         <is>
           <t>A</t>
@@ -8784,7 +8874,7 @@
       <c r="O527" s="4" t="n"/>
       <c r="Q527" s="4" t="n"/>
     </row>
-    <row r="528" ht="15" customHeight="1">
+    <row r="528" hidden="1" ht="15" customHeight="1" s="140">
       <c r="F528" t="inlineStr">
         <is>
           <t>A</t>
@@ -8793,7 +8883,7 @@
       <c r="O528" s="4" t="n"/>
       <c r="Q528" s="4" t="n"/>
     </row>
-    <row r="529" ht="15" customHeight="1">
+    <row r="529" hidden="1" ht="15" customHeight="1" s="140">
       <c r="F529" t="inlineStr">
         <is>
           <t>A</t>
@@ -8802,8 +8892,25 @@
       <c r="O529" s="4" t="n"/>
       <c r="Q529" s="4" t="n"/>
     </row>
+    <row r="530" hidden="1" ht="15" customHeight="1" s="140">
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O530" s="4" t="n"/>
+      <c r="Q530" s="4" t="n"/>
+    </row>
+    <row r="531" hidden="1" ht="15" customHeight="1" s="140">
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O531" s="4" t="n"/>
+      <c r="Q531" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B539"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
